--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1845,6 +1845,8 @@
           <t>med kapsel</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Hagen, Södra Hagen, Vstm</t>
@@ -1901,7 +1903,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fjolårskapslar.</t>
+          <t>Fjolårskapslar. Anna Hammars fynd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,6 +1912,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3858,7 +3861,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5112,7 +5115,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3756,10 +3756,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135060672</v>
+        <v>135143988</v>
       </c>
       <c r="B29" t="n">
-        <v>4776</v>
+        <v>57162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,39 +3767,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499518</v>
+        <v>499426</v>
       </c>
       <c r="R29" t="n">
-        <v>6621482</v>
+        <v>6621880</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3826,22 +3837,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppflog tupp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3861,17 +3877,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135060532</v>
+        <v>135060672</v>
       </c>
       <c r="B30" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3879,21 +3895,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3908,10 +3924,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499516</v>
+        <v>499518</v>
       </c>
       <c r="R30" t="n">
-        <v>6621486</v>
+        <v>6621482</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3943,7 +3959,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3953,7 +3969,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3980,52 +3996,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134232496</v>
+        <v>135060532</v>
       </c>
       <c r="B31" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499676</v>
+        <v>499516</v>
       </c>
       <c r="R31" t="n">
-        <v>6622345</v>
+        <v>6621486</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4049,17 +4066,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4074,19 +4096,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135061152</v>
+        <v>134232496</v>
       </c>
       <c r="B32" t="n">
         <v>58136</v>
@@ -4119,24 +4141,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499523</v>
+        <v>499676</v>
       </c>
       <c r="R32" t="n">
-        <v>6621614</v>
+        <v>6622345</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4160,22 +4177,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4190,19 +4202,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135063205</v>
+        <v>135061152</v>
       </c>
       <c r="B33" t="n">
         <v>58136</v>
@@ -4237,19 +4249,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499625</v>
+        <v>499523</v>
       </c>
       <c r="R33" t="n">
-        <v>6622247</v>
+        <v>6621614</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4281,7 +4293,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4291,7 +4303,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4318,7 +4330,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135064184</v>
+        <v>135063205</v>
       </c>
       <c r="B34" t="n">
         <v>58136</v>
@@ -4346,22 +4358,26 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499579</v>
+        <v>499625</v>
       </c>
       <c r="R34" t="n">
-        <v>6622252</v>
+        <v>6622247</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4393,7 +4409,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4419,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,39 +4446,35 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135059398</v>
+        <v>135064184</v>
       </c>
       <c r="B35" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -4470,14 +4482,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499378</v>
+        <v>499579</v>
       </c>
       <c r="R35" t="n">
-        <v>6621540</v>
+        <v>6622251</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4509,7 +4521,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4519,7 +4531,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,7 +4558,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135063052</v>
+        <v>135059398</v>
       </c>
       <c r="B36" t="n">
         <v>58131</v>
@@ -4576,7 +4588,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4586,14 +4598,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499604</v>
+        <v>499378</v>
       </c>
       <c r="R36" t="n">
-        <v>6622206</v>
+        <v>6621540</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4625,7 +4637,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4635,7 +4647,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,7 +4674,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135063221</v>
+        <v>135063052</v>
       </c>
       <c r="B37" t="n">
         <v>58131</v>
@@ -4702,14 +4714,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499629</v>
+        <v>499604</v>
       </c>
       <c r="R37" t="n">
-        <v>6622247</v>
+        <v>6622206</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4741,7 +4753,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4751,7 +4763,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4778,7 +4790,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135063830</v>
+        <v>135063221</v>
       </c>
       <c r="B38" t="n">
         <v>58131</v>
@@ -4822,10 +4834,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499665</v>
+        <v>499629</v>
       </c>
       <c r="R38" t="n">
-        <v>6622296</v>
+        <v>6622247</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4857,7 +4869,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4867,7 +4879,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4894,7 +4906,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135064196</v>
+        <v>135063830</v>
       </c>
       <c r="B39" t="n">
         <v>58131</v>
@@ -4934,14 +4946,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499579</v>
+        <v>499665</v>
       </c>
       <c r="R39" t="n">
-        <v>6622252</v>
+        <v>6622296</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4973,7 +4985,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4983,7 +4995,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5010,10 +5022,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135060640</v>
+        <v>135064196</v>
       </c>
       <c r="B40" t="n">
-        <v>5201</v>
+        <v>58131</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5021,16 +5033,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5038,22 +5050,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499509</v>
+        <v>499579</v>
       </c>
       <c r="R40" t="n">
-        <v>6621492</v>
+        <v>6622251</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5085,7 +5101,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5095,7 +5111,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5115,17 +5131,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135059764</v>
+        <v>135060640</v>
       </c>
       <c r="B41" t="n">
-        <v>8449</v>
+        <v>5201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5133,21 +5149,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5162,10 +5178,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499467</v>
+        <v>499509</v>
       </c>
       <c r="R41" t="n">
-        <v>6621437</v>
+        <v>6621492</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5197,7 +5213,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5207,7 +5223,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5234,38 +5250,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135059416</v>
+        <v>135059764</v>
       </c>
       <c r="B42" t="n">
-        <v>56706</v>
+        <v>8449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>206046</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5274,10 +5290,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499365</v>
+        <v>499467</v>
       </c>
       <c r="R42" t="n">
-        <v>6621528</v>
+        <v>6621437</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5309,7 +5325,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5319,7 +5335,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5346,7 +5362,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135062618</v>
+        <v>135059416</v>
       </c>
       <c r="B43" t="n">
         <v>56706</v>
@@ -5382,14 +5398,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499537</v>
+        <v>499365</v>
       </c>
       <c r="R43" t="n">
-        <v>6622009</v>
+        <v>6621528</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5421,7 +5437,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5431,7 +5447,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5458,52 +5474,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133925272</v>
+        <v>135062618</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>56706</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>206046</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499669</v>
+        <v>499537</v>
       </c>
       <c r="R44" t="n">
-        <v>6622001</v>
+        <v>6622009</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5527,27 +5544,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5562,19 +5574,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134232494</v>
+        <v>133925272</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5613,13 +5625,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499476</v>
+        <v>499669</v>
       </c>
       <c r="R45" t="n">
-        <v>6622065</v>
+        <v>6622001</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5646,9 +5658,19 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5680,7 +5702,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135059471</v>
+        <v>134232494</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5713,29 +5735,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499368</v>
+        <v>499476</v>
       </c>
       <c r="R46" t="n">
-        <v>6621511</v>
+        <v>6622065</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5759,22 +5771,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5789,19 +5796,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135060107</v>
+        <v>135059471</v>
       </c>
       <c r="B47" t="n">
         <v>99112</v>
@@ -5831,7 +5838,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5850,10 +5857,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499479</v>
+        <v>499368</v>
       </c>
       <c r="R47" t="n">
-        <v>6621502</v>
+        <v>6621511</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5885,7 +5892,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5895,7 +5902,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5922,7 +5929,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135060756</v>
+        <v>135060107</v>
       </c>
       <c r="B48" t="n">
         <v>99112</v>
@@ -5952,7 +5959,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5971,10 +5978,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499547</v>
+        <v>499479</v>
       </c>
       <c r="R48" t="n">
-        <v>6621511</v>
+        <v>6621502</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6006,7 +6013,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6016,7 +6023,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6043,7 +6050,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135061272</v>
+        <v>135060756</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -6073,7 +6080,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6092,10 +6099,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499557</v>
+        <v>499547</v>
       </c>
       <c r="R49" t="n">
-        <v>6621707</v>
+        <v>6621511</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6127,7 +6134,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6137,7 +6144,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6164,7 +6171,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135061286</v>
+        <v>135061272</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -6194,7 +6201,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6213,10 +6220,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499553</v>
+        <v>499557</v>
       </c>
       <c r="R50" t="n">
-        <v>6621728</v>
+        <v>6621707</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6248,7 +6255,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6258,7 +6265,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6285,7 +6292,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135061473</v>
+        <v>135061286</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -6315,30 +6322,32 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499542</v>
+        <v>499553</v>
       </c>
       <c r="R51" t="n">
-        <v>6621615</v>
+        <v>6621728</v>
       </c>
       <c r="S51" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6365,37 +6374,46 @@
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135061528</v>
+        <v>135061473</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -6425,32 +6443,30 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499602</v>
+        <v>499542</v>
       </c>
       <c r="R52" t="n">
-        <v>6621752</v>
+        <v>6621615</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6477,46 +6493,37 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135061587</v>
+        <v>135061528</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6546,7 +6553,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6565,10 +6572,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499604</v>
+        <v>499602</v>
       </c>
       <c r="R53" t="n">
-        <v>6621788</v>
+        <v>6621752</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6600,7 +6607,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6610,7 +6617,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6637,7 +6644,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135061709</v>
+        <v>135061587</v>
       </c>
       <c r="B54" t="n">
         <v>99112</v>
@@ -6667,7 +6674,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6686,10 +6693,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499581</v>
+        <v>499604</v>
       </c>
       <c r="R54" t="n">
-        <v>6621818</v>
+        <v>6621788</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6721,7 +6728,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6731,7 +6738,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6758,7 +6765,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135062653</v>
+        <v>135061709</v>
       </c>
       <c r="B55" t="n">
         <v>99112</v>
@@ -6788,7 +6795,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6803,14 +6810,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499548</v>
+        <v>499581</v>
       </c>
       <c r="R55" t="n">
-        <v>6622078</v>
+        <v>6621818</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6842,7 +6849,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6852,7 +6859,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6879,7 +6886,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135064670</v>
+        <v>135062653</v>
       </c>
       <c r="B56" t="n">
         <v>99112</v>
@@ -6909,7 +6916,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6928,10 +6935,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499511</v>
+        <v>499548</v>
       </c>
       <c r="R56" t="n">
-        <v>6622238</v>
+        <v>6622078</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6963,7 +6970,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6973,7 +6980,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7000,10 +7007,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135059208</v>
+        <v>135064670</v>
       </c>
       <c r="B57" t="n">
-        <v>99219</v>
+        <v>99112</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7011,21 +7018,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7040,19 +7047,19 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499387</v>
+        <v>499511</v>
       </c>
       <c r="R57" t="n">
-        <v>6621650</v>
+        <v>6622238</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7084,7 +7091,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7094,7 +7101,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7121,10 +7128,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135061615</v>
+        <v>135138158</v>
       </c>
       <c r="B58" t="n">
-        <v>111153</v>
+        <v>99112</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7132,27 +7139,36 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220240</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7161,10 +7177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499604</v>
+        <v>499412</v>
       </c>
       <c r="R58" t="n">
-        <v>6621787</v>
+        <v>6621454</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7191,27 +7207,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7231,17 +7242,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135063768</v>
+        <v>135059208</v>
       </c>
       <c r="B59" t="n">
-        <v>98060</v>
+        <v>99219</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7249,34 +7260,48 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499655</v>
+        <v>499387</v>
       </c>
       <c r="R59" t="n">
-        <v>6622288</v>
+        <v>6621650</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7308,7 +7333,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7318,7 +7343,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7338,17 +7363,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135063876</v>
+        <v>135061615</v>
       </c>
       <c r="B60" t="n">
-        <v>99472</v>
+        <v>111153</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7356,16 +7381,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222812</v>
+        <v>220240</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7374,16 +7399,21 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>499672</v>
+        <v>499604</v>
       </c>
       <c r="R60" t="n">
-        <v>6622314</v>
+        <v>6621787</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7415,7 +7445,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7425,7 +7455,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7452,10 +7487,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134232497</v>
+        <v>135063768</v>
       </c>
       <c r="B61" t="n">
-        <v>80438</v>
+        <v>98060</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7463,41 +7498,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>499572</v>
+        <v>499655</v>
       </c>
       <c r="R61" t="n">
-        <v>6622131</v>
+        <v>6622288</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7521,17 +7552,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7546,22 +7582,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135063104</v>
+        <v>135063876</v>
       </c>
       <c r="B62" t="n">
-        <v>80438</v>
+        <v>99472</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7569,21 +7605,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>222812</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7593,10 +7629,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>499616</v>
+        <v>499672</v>
       </c>
       <c r="R62" t="n">
-        <v>6622213</v>
+        <v>6622314</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7628,7 +7664,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7638,12 +7674,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Vid basen av hänsynsasp.</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7670,7 +7701,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135063382</v>
+        <v>134232497</v>
       </c>
       <c r="B63" t="n">
         <v>80438</v>
@@ -7698,20 +7729,24 @@
           <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>499630</v>
+        <v>499572</v>
       </c>
       <c r="R63" t="n">
-        <v>6622258</v>
+        <v>6622131</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7735,27 +7770,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Basen på grav asp, ej hänsynssnitslad.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7770,15 +7795,239 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135063104</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>499616</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6622213</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Vid basen av hänsynsasp.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
           <t>Therese Steiner</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
+      <c r="AX64" t="inlineStr">
         <is>
           <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135063382</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>499630</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6622258</v>
+      </c>
+      <c r="S65" t="n">
+        <v>20</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Basen på grav asp, ej hänsynssnitslad.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Therese Steiner, Anna Hammar</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8029,6 +8029,235 @@
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135155821</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Bockhällen, Bockhällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>499869</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6620679</v>
+      </c>
+      <c r="S66" t="n">
+        <v>20</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fjäder.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135155628</v>
+      </c>
+      <c r="B67" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>499733</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6620805</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -4489,7 +4489,7 @@
         <v>499579</v>
       </c>
       <c r="R35" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -5069,7 +5069,7 @@
         <v>499579</v>
       </c>
       <c r="R40" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4489,7 +4489,7 @@
         <v>499579</v>
       </c>
       <c r="R35" t="n">
-        <v>6622252</v>
+        <v>6622251</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -5069,7 +5069,7 @@
         <v>499579</v>
       </c>
       <c r="R40" t="n">
-        <v>6622252</v>
+        <v>6622251</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1075,7 +1075,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135023647</v>
+        <v>135031428</v>
       </c>
       <c r="B6" t="n">
         <v>57162</v>
@@ -1104,31 +1104,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497636</v>
+        <v>497530</v>
       </c>
       <c r="R6" t="n">
-        <v>6621917</v>
+        <v>6621896</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1152,17 +1145,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fjäder från tjädertupp.</t>
+          <t>Vid rotvälta</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,38 +1176,23 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Våtmark med barrträd</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135031428</v>
+        <v>135032570</v>
       </c>
       <c r="B7" t="n">
         <v>57162</v>
@@ -1232,10 +1220,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1244,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497530</v>
+        <v>497665</v>
       </c>
       <c r="R7" t="n">
-        <v>6621896</v>
+        <v>6621899</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1279,7 +1281,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1289,12 +1291,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vid rotvälta</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,7 +1318,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135032570</v>
+        <v>135033089</v>
       </c>
       <c r="B8" t="n">
         <v>57162</v>
@@ -1361,7 +1358,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1375,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497665</v>
+        <v>497769</v>
       </c>
       <c r="R8" t="n">
-        <v>6621899</v>
+        <v>6621851</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1410,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1417,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fjäder och färsk spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135033089</v>
+        <v>135033156</v>
       </c>
       <c r="B9" t="n">
         <v>57162</v>
@@ -1475,24 +1477,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1501,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497769</v>
+        <v>497764</v>
       </c>
       <c r="R9" t="n">
-        <v>6621851</v>
+        <v>6621865</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1536,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fjäder och färsk spillning</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135033156</v>
+        <v>135032906</v>
       </c>
       <c r="B10" t="n">
-        <v>57162</v>
+        <v>8449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,39 +1572,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497764</v>
+        <v>497759</v>
       </c>
       <c r="R10" t="n">
-        <v>6621865</v>
+        <v>6621852</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1653,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135032906</v>
+        <v>135063650</v>
       </c>
       <c r="B11" t="n">
-        <v>8449</v>
+        <v>96629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,42 +1684,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497759</v>
+        <v>499668</v>
       </c>
       <c r="R11" t="n">
-        <v>6621852</v>
+        <v>6622263</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1760,22 +1754,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjolårskapslar. Anna Hammars fynd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,6 +1783,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135063650</v>
+        <v>135059885</v>
       </c>
       <c r="B12" t="n">
-        <v>96629</v>
+        <v>92370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,53 +1813,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>4217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499668</v>
+        <v>499491</v>
       </c>
       <c r="R12" t="n">
-        <v>6622263</v>
+        <v>6621469</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,7 +1872,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,12 +1882,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fjolårskapslar. Anna Hammars fynd.</t>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,7 +1896,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1931,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135059885</v>
+        <v>135060163</v>
       </c>
       <c r="B13" t="n">
-        <v>92370</v>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,21 +1925,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,10 +1949,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499491</v>
+        <v>499498</v>
       </c>
       <c r="R13" t="n">
-        <v>6621469</v>
+        <v>6621496</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2001,7 +1984,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,12 +1994,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På låga av tall</t>
+          <t>På 2 granlågor</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,7 +2026,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135060163</v>
+        <v>135060941</v>
       </c>
       <c r="B14" t="n">
         <v>91937</v>
@@ -2072,19 +2055,22 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499498</v>
+        <v>499512</v>
       </c>
       <c r="R14" t="n">
-        <v>6621496</v>
+        <v>6621487</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2111,51 +2097,37 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På 2 granlågor</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135060941</v>
+        <v>135063711</v>
       </c>
       <c r="B15" t="n">
         <v>91937</v>
@@ -2184,22 +2156,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499512</v>
+        <v>499668</v>
       </c>
       <c r="R15" t="n">
-        <v>6621487</v>
+        <v>6622269</v>
       </c>
       <c r="S15" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,40 +2195,49 @@
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135063711</v>
+        <v>135060050</v>
       </c>
       <c r="B16" t="n">
-        <v>91937</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,34 +2245,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499668</v>
+        <v>499490</v>
       </c>
       <c r="R16" t="n">
-        <v>6622269</v>
+        <v>6621488</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2326,7 +2309,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2319,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födohack på låga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,7 +2351,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135060050</v>
+        <v>135060358</v>
       </c>
       <c r="B17" t="n">
         <v>57972</v>
@@ -2403,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499490</v>
+        <v>499534</v>
       </c>
       <c r="R17" t="n">
-        <v>6621488</v>
+        <v>6621485</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2438,7 +2426,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,12 +2436,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Födohack på låga.</t>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,7 +2468,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135060358</v>
+        <v>135064630</v>
       </c>
       <c r="B18" t="n">
         <v>57972</v>
@@ -2516,14 +2504,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499534</v>
+        <v>499518</v>
       </c>
       <c r="R18" t="n">
-        <v>6621485</v>
+        <v>6622257</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2555,7 +2543,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,12 +2553,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:32</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På död gran.</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,7 +2580,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135064630</v>
+        <v>135064766</v>
       </c>
       <c r="B19" t="n">
         <v>57972</v>
@@ -2637,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499518</v>
+        <v>499448</v>
       </c>
       <c r="R19" t="n">
-        <v>6622257</v>
+        <v>6622215</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2672,7 +2655,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2682,7 +2665,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,27 +2692,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135064766</v>
+        <v>135061441</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2740,19 +2723,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499448</v>
+        <v>499547</v>
       </c>
       <c r="R20" t="n">
-        <v>6622215</v>
+        <v>6621734</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2784,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2794,7 +2777,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och små hackhål med savflöde i tall. Svårt att se på bild. Tallen utmärkt med rött band.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2821,38 +2809,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135061441</v>
+        <v>135059028</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2861,13 +2849,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499547</v>
+        <v>499383</v>
       </c>
       <c r="R21" t="n">
-        <v>6621734</v>
+        <v>6621640</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2896,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2906,12 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och små hackhål med savflöde i tall. Svårt att se på bild. Tallen utmärkt med rött band.</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,7 +2921,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135059028</v>
+        <v>135059664</v>
       </c>
       <c r="B22" t="n">
         <v>57162</v>
@@ -2974,17 +2957,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergsfallet, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499383</v>
+        <v>499413</v>
       </c>
       <c r="R22" t="n">
-        <v>6621640</v>
+        <v>6621371</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3013,7 +2996,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3023,7 +3006,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,7 +3033,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135059664</v>
+        <v>135061981</v>
       </c>
       <c r="B23" t="n">
         <v>57162</v>
@@ -3086,14 +3069,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartbergsfallet, Lindes sn, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499413</v>
+        <v>499563</v>
       </c>
       <c r="R23" t="n">
-        <v>6621371</v>
+        <v>6621889</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3125,7 +3108,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3135,7 +3118,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på häll bredvid hygget</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,7 +3150,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135061981</v>
+        <v>135062004</v>
       </c>
       <c r="B24" t="n">
         <v>57162</v>
@@ -3202,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499563</v>
+        <v>499575</v>
       </c>
       <c r="R24" t="n">
-        <v>6621889</v>
+        <v>6621902</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3237,7 +3225,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3247,12 +3235,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt på häll bredvid hygget</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3279,7 +3262,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135062004</v>
+        <v>135062059</v>
       </c>
       <c r="B25" t="n">
         <v>57162</v>
@@ -3307,22 +3290,36 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499575</v>
+        <v>499546</v>
       </c>
       <c r="R25" t="n">
-        <v>6621902</v>
+        <v>6621943</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3354,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3364,7 +3361,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färsk fjäder fr tupp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3391,7 +3393,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135062059</v>
+        <v>135062640</v>
       </c>
       <c r="B26" t="n">
         <v>57162</v>
@@ -3419,24 +3421,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3445,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499546</v>
+        <v>499562</v>
       </c>
       <c r="R26" t="n">
-        <v>6621943</v>
+        <v>6622064</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3480,7 +3468,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3490,12 +3478,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färsk fjäder fr tupp.</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3522,7 +3510,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135062640</v>
+        <v>135064589</v>
       </c>
       <c r="B27" t="n">
         <v>57162</v>
@@ -3562,10 +3550,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499562</v>
+        <v>499561</v>
       </c>
       <c r="R27" t="n">
-        <v>6622064</v>
+        <v>6622261</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3597,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3607,12 +3595,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>I övergiven myrstack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,7 +3627,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135064589</v>
+        <v>135143988</v>
       </c>
       <c r="B28" t="n">
         <v>57162</v>
@@ -3667,22 +3655,33 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499561</v>
+        <v>499426</v>
       </c>
       <c r="R28" t="n">
-        <v>6622261</v>
+        <v>6621880</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3709,27 +3708,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I övergiven myrstack.</t>
+          <t>Uppflog tupp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,17 +3748,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135143988</v>
+        <v>135060672</v>
       </c>
       <c r="B29" t="n">
-        <v>57162</v>
+        <v>4776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,50 +3766,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499426</v>
+        <v>499518</v>
       </c>
       <c r="R29" t="n">
-        <v>6621880</v>
+        <v>6621482</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3837,27 +3825,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Uppflog tupp</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,17 +3860,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135060672</v>
+        <v>135060532</v>
       </c>
       <c r="B30" t="n">
-        <v>4776</v>
+        <v>5181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,21 +3878,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3924,10 +3907,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499518</v>
+        <v>499516</v>
       </c>
       <c r="R30" t="n">
-        <v>6621482</v>
+        <v>6621486</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3959,7 +3942,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3969,7 +3952,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3996,53 +3979,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135060532</v>
+        <v>134232496</v>
       </c>
       <c r="B31" t="n">
-        <v>5181</v>
+        <v>58136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499516</v>
+        <v>499676</v>
       </c>
       <c r="R31" t="n">
-        <v>6621486</v>
+        <v>6622345</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4066,22 +4048,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4096,19 +4073,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134232496</v>
+        <v>135061152</v>
       </c>
       <c r="B32" t="n">
         <v>58136</v>
@@ -4141,19 +4118,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499676</v>
+        <v>499523</v>
       </c>
       <c r="R32" t="n">
-        <v>6622345</v>
+        <v>6621614</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4177,17 +4159,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4202,19 +4189,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135061152</v>
+        <v>135063205</v>
       </c>
       <c r="B33" t="n">
         <v>58136</v>
@@ -4249,19 +4236,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499523</v>
+        <v>499625</v>
       </c>
       <c r="R33" t="n">
-        <v>6621614</v>
+        <v>6622247</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4293,7 +4280,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4303,7 +4290,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4330,7 +4317,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135063205</v>
+        <v>135064184</v>
       </c>
       <c r="B34" t="n">
         <v>58136</v>
@@ -4358,26 +4345,22 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499625</v>
+        <v>499579</v>
       </c>
       <c r="R34" t="n">
-        <v>6622247</v>
+        <v>6622252</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4409,7 +4392,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4419,7 +4402,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4446,35 +4429,39 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135064184</v>
+        <v>135059398</v>
       </c>
       <c r="B35" t="n">
-        <v>58136</v>
+        <v>58131</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -4482,14 +4469,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499579</v>
+        <v>499378</v>
       </c>
       <c r="R35" t="n">
-        <v>6622251</v>
+        <v>6621540</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4521,7 +4508,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4531,7 +4518,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4558,7 +4545,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135059398</v>
+        <v>135063052</v>
       </c>
       <c r="B36" t="n">
         <v>58131</v>
@@ -4588,7 +4575,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4598,14 +4585,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499378</v>
+        <v>499604</v>
       </c>
       <c r="R36" t="n">
-        <v>6621540</v>
+        <v>6622206</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4637,7 +4624,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4647,7 +4634,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4674,7 +4661,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135063052</v>
+        <v>135063221</v>
       </c>
       <c r="B37" t="n">
         <v>58131</v>
@@ -4714,14 +4701,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499604</v>
+        <v>499629</v>
       </c>
       <c r="R37" t="n">
-        <v>6622206</v>
+        <v>6622247</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4753,7 +4740,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4763,7 +4750,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4790,7 +4777,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135063221</v>
+        <v>135063830</v>
       </c>
       <c r="B38" t="n">
         <v>58131</v>
@@ -4834,10 +4821,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499629</v>
+        <v>499665</v>
       </c>
       <c r="R38" t="n">
-        <v>6622247</v>
+        <v>6622296</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4869,7 +4856,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4879,7 +4866,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4906,7 +4893,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135063830</v>
+        <v>135064196</v>
       </c>
       <c r="B39" t="n">
         <v>58131</v>
@@ -4946,14 +4933,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499665</v>
+        <v>499579</v>
       </c>
       <c r="R39" t="n">
-        <v>6622296</v>
+        <v>6622252</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4985,7 +4972,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4995,7 +4982,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5022,10 +5009,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135064196</v>
+        <v>135060640</v>
       </c>
       <c r="B40" t="n">
-        <v>58131</v>
+        <v>5201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,16 +5020,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103023</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5050,26 +5037,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499579</v>
+        <v>499509</v>
       </c>
       <c r="R40" t="n">
-        <v>6622251</v>
+        <v>6621492</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5101,7 +5084,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5111,7 +5094,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5131,17 +5114,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135060640</v>
+        <v>135059764</v>
       </c>
       <c r="B41" t="n">
-        <v>5201</v>
+        <v>8449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,21 +5132,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5178,10 +5161,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499509</v>
+        <v>499467</v>
       </c>
       <c r="R41" t="n">
-        <v>6621492</v>
+        <v>6621437</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5213,7 +5196,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5223,7 +5206,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5250,38 +5233,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135059764</v>
+        <v>135059416</v>
       </c>
       <c r="B42" t="n">
-        <v>8449</v>
+        <v>56706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106554</v>
+        <v>206046</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5290,10 +5273,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499467</v>
+        <v>499365</v>
       </c>
       <c r="R42" t="n">
-        <v>6621437</v>
+        <v>6621528</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5325,7 +5308,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5335,7 +5318,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5362,7 +5345,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135059416</v>
+        <v>135062618</v>
       </c>
       <c r="B43" t="n">
         <v>56706</v>
@@ -5398,14 +5381,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499365</v>
+        <v>499537</v>
       </c>
       <c r="R43" t="n">
-        <v>6621528</v>
+        <v>6622009</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5437,7 +5420,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5447,7 +5430,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5474,53 +5457,52 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135062618</v>
+        <v>133925272</v>
       </c>
       <c r="B44" t="n">
-        <v>56706</v>
+        <v>99112</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206046</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499537</v>
+        <v>499669</v>
       </c>
       <c r="R44" t="n">
-        <v>6622009</v>
+        <v>6622001</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5544,22 +5526,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5574,19 +5561,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133925272</v>
+        <v>134232494</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5625,13 +5612,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499669</v>
+        <v>499476</v>
       </c>
       <c r="R45" t="n">
-        <v>6622001</v>
+        <v>6622065</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5658,19 +5645,9 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5702,7 +5679,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134232494</v>
+        <v>135059471</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5735,19 +5712,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499476</v>
+        <v>499368</v>
       </c>
       <c r="R46" t="n">
-        <v>6622065</v>
+        <v>6621511</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5771,17 +5758,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5796,19 +5788,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135059471</v>
+        <v>135060107</v>
       </c>
       <c r="B47" t="n">
         <v>99112</v>
@@ -5838,7 +5830,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5857,10 +5849,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499368</v>
+        <v>499479</v>
       </c>
       <c r="R47" t="n">
-        <v>6621511</v>
+        <v>6621502</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5892,7 +5884,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5902,7 +5894,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5929,7 +5921,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135060107</v>
+        <v>135060756</v>
       </c>
       <c r="B48" t="n">
         <v>99112</v>
@@ -5959,7 +5951,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5978,10 +5970,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499479</v>
+        <v>499547</v>
       </c>
       <c r="R48" t="n">
-        <v>6621502</v>
+        <v>6621511</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6013,7 +6005,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6023,7 +6015,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6050,7 +6042,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135060756</v>
+        <v>135061272</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -6080,7 +6072,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6099,10 +6091,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499547</v>
+        <v>499557</v>
       </c>
       <c r="R49" t="n">
-        <v>6621511</v>
+        <v>6621707</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6134,7 +6126,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6144,7 +6136,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6171,7 +6163,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135061272</v>
+        <v>135061286</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -6201,7 +6193,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6220,10 +6212,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499557</v>
+        <v>499553</v>
       </c>
       <c r="R50" t="n">
-        <v>6621707</v>
+        <v>6621728</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6255,7 +6247,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6265,7 +6257,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6292,7 +6284,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135061286</v>
+        <v>135061473</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -6322,32 +6314,30 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499553</v>
+        <v>499542</v>
       </c>
       <c r="R51" t="n">
-        <v>6621728</v>
+        <v>6621615</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6374,46 +6364,37 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135061473</v>
+        <v>135061528</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -6443,30 +6424,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499542</v>
+        <v>499602</v>
       </c>
       <c r="R52" t="n">
-        <v>6621615</v>
+        <v>6621752</v>
       </c>
       <c r="S52" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6493,37 +6476,46 @@
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135061528</v>
+        <v>135061587</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6553,7 +6545,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6572,10 +6564,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499602</v>
+        <v>499604</v>
       </c>
       <c r="R53" t="n">
-        <v>6621752</v>
+        <v>6621788</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6607,7 +6599,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6617,7 +6609,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6644,7 +6636,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135061587</v>
+        <v>135061709</v>
       </c>
       <c r="B54" t="n">
         <v>99112</v>
@@ -6674,7 +6666,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6693,10 +6685,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499604</v>
+        <v>499581</v>
       </c>
       <c r="R54" t="n">
-        <v>6621788</v>
+        <v>6621818</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6728,7 +6720,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6738,7 +6730,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6765,7 +6757,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135061709</v>
+        <v>135062653</v>
       </c>
       <c r="B55" t="n">
         <v>99112</v>
@@ -6795,7 +6787,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6810,14 +6802,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499581</v>
+        <v>499548</v>
       </c>
       <c r="R55" t="n">
-        <v>6621818</v>
+        <v>6622078</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6849,7 +6841,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6859,7 +6851,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6886,7 +6878,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135062653</v>
+        <v>135064670</v>
       </c>
       <c r="B56" t="n">
         <v>99112</v>
@@ -6916,7 +6908,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6935,10 +6927,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499548</v>
+        <v>499511</v>
       </c>
       <c r="R56" t="n">
-        <v>6622078</v>
+        <v>6622238</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6970,7 +6962,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6980,7 +6972,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7007,7 +6999,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135064670</v>
+        <v>135138158</v>
       </c>
       <c r="B57" t="n">
         <v>99112</v>
@@ -7037,7 +7029,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7052,14 +7044,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499511</v>
+        <v>499412</v>
       </c>
       <c r="R57" t="n">
-        <v>6622238</v>
+        <v>6621454</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7086,22 +7078,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7121,17 +7113,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135138158</v>
+        <v>135059208</v>
       </c>
       <c r="B58" t="n">
-        <v>99112</v>
+        <v>99219</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7139,26 +7131,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7168,7 +7160,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7177,10 +7169,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499412</v>
+        <v>499387</v>
       </c>
       <c r="R58" t="n">
-        <v>6621454</v>
+        <v>6621650</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7207,22 +7199,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7242,17 +7234,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135059208</v>
+        <v>135061615</v>
       </c>
       <c r="B59" t="n">
-        <v>99219</v>
+        <v>111153</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7260,33 +7252,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219847</v>
+        <v>220240</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7298,10 +7281,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499387</v>
+        <v>499604</v>
       </c>
       <c r="R59" t="n">
-        <v>6621650</v>
+        <v>6621787</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7333,7 +7316,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7343,7 +7326,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7370,10 +7358,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135061615</v>
+        <v>135063768</v>
       </c>
       <c r="B60" t="n">
-        <v>111153</v>
+        <v>98060</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7381,16 +7369,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220240</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7399,21 +7387,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>499604</v>
+        <v>499655</v>
       </c>
       <c r="R60" t="n">
-        <v>6621787</v>
+        <v>6622288</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7445,7 +7428,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7455,12 +7438,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7487,10 +7465,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135063768</v>
+        <v>135063876</v>
       </c>
       <c r="B61" t="n">
-        <v>98060</v>
+        <v>99472</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7498,16 +7476,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>222812</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7522,10 +7500,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>499655</v>
+        <v>499672</v>
       </c>
       <c r="R61" t="n">
-        <v>6622288</v>
+        <v>6622314</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7557,7 +7535,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7567,7 +7545,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7594,10 +7572,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135063876</v>
+        <v>134232497</v>
       </c>
       <c r="B62" t="n">
-        <v>99472</v>
+        <v>80438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7605,37 +7583,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222812</v>
+        <v>229497</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>499672</v>
+        <v>499572</v>
       </c>
       <c r="R62" t="n">
-        <v>6622314</v>
+        <v>6622131</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7659,22 +7641,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7689,19 +7666,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134232497</v>
+        <v>135063104</v>
       </c>
       <c r="B63" t="n">
         <v>80438</v>
@@ -7729,24 +7706,20 @@
           <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>499572</v>
+        <v>499616</v>
       </c>
       <c r="R63" t="n">
-        <v>6622131</v>
+        <v>6622213</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7770,17 +7743,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Vid basen av hänsynsasp.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7795,19 +7778,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135063104</v>
+        <v>135063382</v>
       </c>
       <c r="B64" t="n">
         <v>80438</v>
@@ -7842,10 +7825,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>499616</v>
+        <v>499630</v>
       </c>
       <c r="R64" t="n">
-        <v>6622213</v>
+        <v>6622258</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7877,7 +7860,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7887,12 +7870,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Vid basen av hänsynsasp.</t>
+          <t>Basen på grav asp, ej hänsynssnitslad.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7919,10 +7902,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135063382</v>
+        <v>135155821</v>
       </c>
       <c r="B65" t="n">
-        <v>80438</v>
+        <v>57162</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7930,34 +7913,49 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bockhällen, Bockhällen, Vstm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>499630</v>
+        <v>499869</v>
       </c>
       <c r="R65" t="n">
-        <v>6622258</v>
+        <v>6620679</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7984,27 +7982,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Basen på grav asp, ej hänsynssnitslad.</t>
+          <t>Fjäder.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8024,67 +8012,57 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner, Per Arneborn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135155821</v>
+        <v>135155628</v>
       </c>
       <c r="B66" t="n">
-        <v>57162</v>
+        <v>56706</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>206046</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bockhällen, Bockhällen, Vstm</t>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>499869</v>
+        <v>499733</v>
       </c>
       <c r="R66" t="n">
-        <v>6620679</v>
+        <v>6620805</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -8114,14 +8092,19 @@
           <t>2026-07-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Fjäder.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8141,122 +8124,10 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Therese Steiner, Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135155628</v>
-      </c>
-      <c r="B67" t="n">
-        <v>56706</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>206046</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Alces alces</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>499733</v>
-      </c>
-      <c r="R67" t="n">
-        <v>6620805</v>
-      </c>
-      <c r="S67" t="n">
-        <v>20</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Lindesberg</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>08:14</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>08:14</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1075,7 +1075,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135031428</v>
+        <v>135023647</v>
       </c>
       <c r="B6" t="n">
         <v>57162</v>
@@ -1104,24 +1104,31 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497530</v>
+        <v>497636</v>
       </c>
       <c r="R6" t="n">
-        <v>6621896</v>
+        <v>6621917</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1145,27 +1152,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vid rotvälta</t>
+          <t>Fjäder från tjädertupp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,23 +1173,38 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Våtmark med barrträd</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135032570</v>
+        <v>135031428</v>
       </c>
       <c r="B7" t="n">
         <v>57162</v>
@@ -1220,24 +1232,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1246,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497665</v>
+        <v>497530</v>
       </c>
       <c r="R7" t="n">
-        <v>6621899</v>
+        <v>6621896</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1281,7 +1279,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1291,7 +1289,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid rotvälta</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135033089</v>
+        <v>135032570</v>
       </c>
       <c r="B8" t="n">
         <v>57162</v>
@@ -1358,7 +1361,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1372,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497769</v>
+        <v>497665</v>
       </c>
       <c r="R8" t="n">
-        <v>6621851</v>
+        <v>6621899</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1407,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,12 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fjäder och färsk spillning</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,7 +1447,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135033156</v>
+        <v>135033089</v>
       </c>
       <c r="B9" t="n">
         <v>57162</v>
@@ -1477,10 +1475,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1489,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497764</v>
+        <v>497769</v>
       </c>
       <c r="R9" t="n">
-        <v>6621865</v>
+        <v>6621851</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1524,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjäder och färsk spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135032906</v>
+        <v>135033156</v>
       </c>
       <c r="B10" t="n">
-        <v>8449</v>
+        <v>57162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,39 +1589,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497759</v>
+        <v>497764</v>
       </c>
       <c r="R10" t="n">
-        <v>6621852</v>
+        <v>6621865</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1636,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135063650</v>
+        <v>135032906</v>
       </c>
       <c r="B11" t="n">
-        <v>96629</v>
+        <v>8449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,53 +1701,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499668</v>
+        <v>497759</v>
       </c>
       <c r="R11" t="n">
-        <v>6622263</v>
+        <v>6621852</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1754,27 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fjolårskapslar. Anna Hammars fynd.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,7 +1784,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135059885</v>
+        <v>135063650</v>
       </c>
       <c r="B12" t="n">
-        <v>92370</v>
+        <v>96629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,37 +1813,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499491</v>
+        <v>499668</v>
       </c>
       <c r="R12" t="n">
-        <v>6621469</v>
+        <v>6622263</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1882,12 +1898,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På låga av tall</t>
+          <t>Fjolårskapslar. Anna Hammars fynd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,6 +1912,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1914,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135060163</v>
+        <v>135059885</v>
       </c>
       <c r="B13" t="n">
-        <v>91937</v>
+        <v>92370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1949,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499498</v>
+        <v>499491</v>
       </c>
       <c r="R13" t="n">
-        <v>6621496</v>
+        <v>6621469</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1984,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1994,12 +2011,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På 2 granlågor</t>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,14 +2036,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135060941</v>
+        <v>135060163</v>
       </c>
       <c r="B14" t="n">
         <v>91937</v>
@@ -2055,22 +2072,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499512</v>
+        <v>499498</v>
       </c>
       <c r="R14" t="n">
-        <v>6621487</v>
+        <v>6621496</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,37 +2111,51 @@
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På 2 granlågor</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135063711</v>
+        <v>135060941</v>
       </c>
       <c r="B15" t="n">
         <v>91937</v>
@@ -2156,19 +2184,22 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499668</v>
+        <v>499512</v>
       </c>
       <c r="R15" t="n">
-        <v>6622269</v>
+        <v>6621487</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2195,49 +2226,40 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135060050</v>
+        <v>135063711</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>91937</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,39 +2267,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499490</v>
+        <v>499668</v>
       </c>
       <c r="R16" t="n">
-        <v>6621488</v>
+        <v>6622269</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2309,7 +2326,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2319,12 +2336,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födohack på låga.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,14 +2356,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135060358</v>
+        <v>135060050</v>
       </c>
       <c r="B17" t="n">
         <v>57972</v>
@@ -2391,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499534</v>
+        <v>499490</v>
       </c>
       <c r="R17" t="n">
-        <v>6621485</v>
+        <v>6621488</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2426,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2436,12 +2448,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>Födohack på låga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,7 +2480,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135064630</v>
+        <v>135060358</v>
       </c>
       <c r="B18" t="n">
         <v>57972</v>
@@ -2504,14 +2516,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499518</v>
+        <v>499534</v>
       </c>
       <c r="R18" t="n">
-        <v>6622257</v>
+        <v>6621485</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2543,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2553,7 +2565,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2580,7 +2597,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135064766</v>
+        <v>135064630</v>
       </c>
       <c r="B19" t="n">
         <v>57972</v>
@@ -2620,10 +2637,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499448</v>
+        <v>499518</v>
       </c>
       <c r="R19" t="n">
-        <v>6622215</v>
+        <v>6622257</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2655,7 +2672,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2665,7 +2682,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2692,27 +2709,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135061441</v>
+        <v>135064766</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2723,19 +2740,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499547</v>
+        <v>499448</v>
       </c>
       <c r="R20" t="n">
-        <v>6621734</v>
+        <v>6622215</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2767,7 +2784,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2777,12 +2794,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och små hackhål med savflöde i tall. Svårt att se på bild. Tallen utmärkt med rött band.</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,38 +2821,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135059028</v>
+        <v>135061441</v>
       </c>
       <c r="B21" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2849,13 +2861,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499383</v>
+        <v>499547</v>
       </c>
       <c r="R21" t="n">
-        <v>6621640</v>
+        <v>6621734</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2884,7 +2896,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2906,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och små hackhål med savflöde i tall. Svårt att se på bild. Tallen utmärkt med rött band.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2921,7 +2938,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135059664</v>
+        <v>135059028</v>
       </c>
       <c r="B22" t="n">
         <v>57162</v>
@@ -2957,17 +2974,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartbergsfallet, Lindes sn, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499413</v>
+        <v>499383</v>
       </c>
       <c r="R22" t="n">
-        <v>6621371</v>
+        <v>6621640</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2996,7 +3013,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,7 +3023,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,7 +3050,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135061981</v>
+        <v>135059664</v>
       </c>
       <c r="B23" t="n">
         <v>57162</v>
@@ -3069,14 +3086,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergsfallet, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499563</v>
+        <v>499413</v>
       </c>
       <c r="R23" t="n">
-        <v>6621889</v>
+        <v>6621371</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3108,7 +3125,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3118,12 +3135,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt på häll bredvid hygget</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,7 +3162,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135062004</v>
+        <v>135061981</v>
       </c>
       <c r="B24" t="n">
         <v>57162</v>
@@ -3190,10 +3202,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499575</v>
+        <v>499563</v>
       </c>
       <c r="R24" t="n">
-        <v>6621902</v>
+        <v>6621889</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3225,7 +3237,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3247,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt på häll bredvid hygget</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,7 +3279,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135062059</v>
+        <v>135062004</v>
       </c>
       <c r="B25" t="n">
         <v>57162</v>
@@ -3290,36 +3307,22 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499546</v>
+        <v>499575</v>
       </c>
       <c r="R25" t="n">
-        <v>6621943</v>
+        <v>6621902</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3351,7 +3354,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,12 +3364,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färsk fjäder fr tupp.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3393,7 +3391,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135062640</v>
+        <v>135062059</v>
       </c>
       <c r="B26" t="n">
         <v>57162</v>
@@ -3421,10 +3419,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3433,10 +3445,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499562</v>
+        <v>499546</v>
       </c>
       <c r="R26" t="n">
-        <v>6622064</v>
+        <v>6621943</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3468,7 +3480,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3478,12 +3490,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Färsk fjäder fr tupp.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,7 +3522,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135064589</v>
+        <v>135062640</v>
       </c>
       <c r="B27" t="n">
         <v>57162</v>
@@ -3550,10 +3562,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499561</v>
+        <v>499562</v>
       </c>
       <c r="R27" t="n">
-        <v>6622261</v>
+        <v>6622064</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3585,7 +3597,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,12 +3607,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I övergiven myrstack.</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3627,7 +3639,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135143988</v>
+        <v>135064589</v>
       </c>
       <c r="B28" t="n">
         <v>57162</v>
@@ -3655,33 +3667,22 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499426</v>
+        <v>499561</v>
       </c>
       <c r="R28" t="n">
-        <v>6621880</v>
+        <v>6622261</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3708,27 +3709,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Uppflog tupp</t>
+          <t>I övergiven myrstack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3748,17 +3749,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135060672</v>
+        <v>135143988</v>
       </c>
       <c r="B29" t="n">
-        <v>4776</v>
+        <v>57162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,39 +3767,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499518</v>
+        <v>499426</v>
       </c>
       <c r="R29" t="n">
-        <v>6621482</v>
+        <v>6621880</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3825,22 +3837,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppflog tupp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,17 +3877,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135060532</v>
+        <v>135060672</v>
       </c>
       <c r="B30" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3878,21 +3895,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3907,10 +3924,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499516</v>
+        <v>499518</v>
       </c>
       <c r="R30" t="n">
-        <v>6621486</v>
+        <v>6621482</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3942,7 +3959,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3952,7 +3969,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3972,59 +3989,60 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134232496</v>
+        <v>135060532</v>
       </c>
       <c r="B31" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499676</v>
+        <v>499516</v>
       </c>
       <c r="R31" t="n">
-        <v>6622345</v>
+        <v>6621486</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4048,17 +4066,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4073,19 +4096,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135061152</v>
+        <v>134232496</v>
       </c>
       <c r="B32" t="n">
         <v>58136</v>
@@ -4118,24 +4141,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499523</v>
+        <v>499676</v>
       </c>
       <c r="R32" t="n">
-        <v>6621614</v>
+        <v>6622345</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4159,22 +4177,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4189,19 +4202,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135063205</v>
+        <v>135061152</v>
       </c>
       <c r="B33" t="n">
         <v>58136</v>
@@ -4236,19 +4249,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499625</v>
+        <v>499523</v>
       </c>
       <c r="R33" t="n">
-        <v>6622247</v>
+        <v>6621614</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4280,7 +4293,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4290,7 +4303,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4317,7 +4330,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135064184</v>
+        <v>135063205</v>
       </c>
       <c r="B34" t="n">
         <v>58136</v>
@@ -4345,22 +4358,26 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499579</v>
+        <v>499625</v>
       </c>
       <c r="R34" t="n">
-        <v>6622252</v>
+        <v>6622247</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4392,7 +4409,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4402,7 +4419,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4429,39 +4446,35 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135059398</v>
+        <v>135064184</v>
       </c>
       <c r="B35" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -4469,14 +4482,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499378</v>
+        <v>499579</v>
       </c>
       <c r="R35" t="n">
-        <v>6621540</v>
+        <v>6622252</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4508,7 +4521,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4518,7 +4531,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4545,7 +4558,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135063052</v>
+        <v>135059398</v>
       </c>
       <c r="B36" t="n">
         <v>58131</v>
@@ -4575,7 +4588,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4585,14 +4598,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499604</v>
+        <v>499378</v>
       </c>
       <c r="R36" t="n">
-        <v>6622206</v>
+        <v>6621540</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4624,7 +4637,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4634,7 +4647,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4661,7 +4674,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135063221</v>
+        <v>135063052</v>
       </c>
       <c r="B37" t="n">
         <v>58131</v>
@@ -4701,14 +4714,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499629</v>
+        <v>499604</v>
       </c>
       <c r="R37" t="n">
-        <v>6622247</v>
+        <v>6622206</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4740,7 +4753,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4750,7 +4763,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4777,7 +4790,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135063830</v>
+        <v>135063221</v>
       </c>
       <c r="B38" t="n">
         <v>58131</v>
@@ -4821,10 +4834,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499665</v>
+        <v>499629</v>
       </c>
       <c r="R38" t="n">
-        <v>6622296</v>
+        <v>6622247</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4856,7 +4869,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4866,7 +4879,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4893,7 +4906,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135064196</v>
+        <v>135063830</v>
       </c>
       <c r="B39" t="n">
         <v>58131</v>
@@ -4933,14 +4946,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499579</v>
+        <v>499665</v>
       </c>
       <c r="R39" t="n">
-        <v>6622252</v>
+        <v>6622296</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4972,7 +4985,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4982,7 +4995,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5009,10 +5022,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135060640</v>
+        <v>135064196</v>
       </c>
       <c r="B40" t="n">
-        <v>5201</v>
+        <v>58131</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5020,16 +5033,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5037,22 +5050,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499509</v>
+        <v>499579</v>
       </c>
       <c r="R40" t="n">
-        <v>6621492</v>
+        <v>6622252</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5084,7 +5101,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5094,7 +5111,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5114,17 +5131,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135059764</v>
+        <v>135060640</v>
       </c>
       <c r="B41" t="n">
-        <v>8449</v>
+        <v>5201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5132,21 +5149,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5161,10 +5178,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499467</v>
+        <v>499509</v>
       </c>
       <c r="R41" t="n">
-        <v>6621437</v>
+        <v>6621492</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5196,7 +5213,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5206,7 +5223,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5233,38 +5250,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135059416</v>
+        <v>135059764</v>
       </c>
       <c r="B42" t="n">
-        <v>56706</v>
+        <v>8449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>206046</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5273,10 +5290,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499365</v>
+        <v>499467</v>
       </c>
       <c r="R42" t="n">
-        <v>6621528</v>
+        <v>6621437</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5308,7 +5325,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5318,7 +5335,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5345,7 +5362,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135062618</v>
+        <v>135059416</v>
       </c>
       <c r="B43" t="n">
         <v>56706</v>
@@ -5381,14 +5398,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499537</v>
+        <v>499365</v>
       </c>
       <c r="R43" t="n">
-        <v>6622009</v>
+        <v>6621528</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5420,7 +5437,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5430,7 +5447,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5457,52 +5474,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133925272</v>
+        <v>135062618</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>56706</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>206046</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499669</v>
+        <v>499537</v>
       </c>
       <c r="R44" t="n">
-        <v>6622001</v>
+        <v>6622009</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5526,27 +5544,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5561,19 +5574,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134232494</v>
+        <v>133925272</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5612,13 +5625,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499476</v>
+        <v>499669</v>
       </c>
       <c r="R45" t="n">
-        <v>6622065</v>
+        <v>6622001</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5645,9 +5658,19 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5679,7 +5702,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135059471</v>
+        <v>134232494</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5712,29 +5735,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499368</v>
+        <v>499476</v>
       </c>
       <c r="R46" t="n">
-        <v>6621511</v>
+        <v>6622065</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5758,22 +5771,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5788,19 +5796,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135060107</v>
+        <v>135059471</v>
       </c>
       <c r="B47" t="n">
         <v>99112</v>
@@ -5830,7 +5838,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5849,10 +5857,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499479</v>
+        <v>499368</v>
       </c>
       <c r="R47" t="n">
-        <v>6621502</v>
+        <v>6621511</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5884,7 +5892,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5894,7 +5902,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5921,7 +5929,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135060756</v>
+        <v>135060107</v>
       </c>
       <c r="B48" t="n">
         <v>99112</v>
@@ -5951,7 +5959,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5970,10 +5978,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499547</v>
+        <v>499479</v>
       </c>
       <c r="R48" t="n">
-        <v>6621511</v>
+        <v>6621502</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6005,7 +6013,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6015,7 +6023,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6042,7 +6050,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135061272</v>
+        <v>135060756</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -6072,7 +6080,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6091,10 +6099,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499557</v>
+        <v>499547</v>
       </c>
       <c r="R49" t="n">
-        <v>6621707</v>
+        <v>6621511</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6126,7 +6134,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6136,7 +6144,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6163,7 +6171,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135061286</v>
+        <v>135061272</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -6193,7 +6201,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6212,10 +6220,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499553</v>
+        <v>499557</v>
       </c>
       <c r="R50" t="n">
-        <v>6621728</v>
+        <v>6621707</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6247,7 +6255,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6257,7 +6265,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6284,7 +6292,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135061473</v>
+        <v>135061286</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -6314,30 +6322,32 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499542</v>
+        <v>499553</v>
       </c>
       <c r="R51" t="n">
-        <v>6621615</v>
+        <v>6621728</v>
       </c>
       <c r="S51" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6364,37 +6374,46 @@
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135061528</v>
+        <v>135061473</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -6424,32 +6443,30 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499602</v>
+        <v>499542</v>
       </c>
       <c r="R52" t="n">
-        <v>6621752</v>
+        <v>6621615</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6476,46 +6493,37 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135061587</v>
+        <v>135061528</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6545,7 +6553,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6564,10 +6572,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499604</v>
+        <v>499602</v>
       </c>
       <c r="R53" t="n">
-        <v>6621788</v>
+        <v>6621752</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6599,7 +6607,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6609,7 +6617,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6636,7 +6644,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135061709</v>
+        <v>135061587</v>
       </c>
       <c r="B54" t="n">
         <v>99112</v>
@@ -6666,7 +6674,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6685,10 +6693,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499581</v>
+        <v>499604</v>
       </c>
       <c r="R54" t="n">
-        <v>6621818</v>
+        <v>6621788</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6720,7 +6728,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6730,7 +6738,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6757,7 +6765,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135062653</v>
+        <v>135061709</v>
       </c>
       <c r="B55" t="n">
         <v>99112</v>
@@ -6787,7 +6795,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6802,14 +6810,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499548</v>
+        <v>499581</v>
       </c>
       <c r="R55" t="n">
-        <v>6622078</v>
+        <v>6621818</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6841,7 +6849,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6851,7 +6859,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6871,14 +6879,14 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135064670</v>
+        <v>135062653</v>
       </c>
       <c r="B56" t="n">
         <v>99112</v>
@@ -6908,7 +6916,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6927,10 +6935,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499511</v>
+        <v>499548</v>
       </c>
       <c r="R56" t="n">
-        <v>6622238</v>
+        <v>6622078</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6962,7 +6970,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6972,7 +6980,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6999,7 +7007,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135138158</v>
+        <v>135064670</v>
       </c>
       <c r="B57" t="n">
         <v>99112</v>
@@ -7029,7 +7037,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7044,14 +7052,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499412</v>
+        <v>499511</v>
       </c>
       <c r="R57" t="n">
-        <v>6621454</v>
+        <v>6622238</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7078,22 +7086,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7113,17 +7121,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135059208</v>
+        <v>135138158</v>
       </c>
       <c r="B58" t="n">
-        <v>99219</v>
+        <v>99112</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7131,26 +7139,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7160,7 +7168,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7169,10 +7177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499387</v>
+        <v>499412</v>
       </c>
       <c r="R58" t="n">
-        <v>6621650</v>
+        <v>6621454</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7199,22 +7207,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7234,17 +7242,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135061615</v>
+        <v>135059208</v>
       </c>
       <c r="B59" t="n">
-        <v>111153</v>
+        <v>99219</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7252,24 +7260,33 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220240</v>
+        <v>219847</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7281,10 +7298,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499604</v>
+        <v>499387</v>
       </c>
       <c r="R59" t="n">
-        <v>6621787</v>
+        <v>6621650</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7316,7 +7333,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7326,12 +7343,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7358,10 +7370,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135063768</v>
+        <v>135061615</v>
       </c>
       <c r="B60" t="n">
-        <v>98060</v>
+        <v>111153</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7369,16 +7381,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>220240</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7387,16 +7399,21 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>499655</v>
+        <v>499604</v>
       </c>
       <c r="R60" t="n">
-        <v>6622288</v>
+        <v>6621787</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7428,7 +7445,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7438,7 +7455,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7465,10 +7487,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135063876</v>
+        <v>135063768</v>
       </c>
       <c r="B61" t="n">
-        <v>99472</v>
+        <v>98060</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7476,16 +7498,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222812</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7500,10 +7522,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>499672</v>
+        <v>499655</v>
       </c>
       <c r="R61" t="n">
-        <v>6622314</v>
+        <v>6622288</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7535,7 +7557,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7545,7 +7567,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7572,10 +7594,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134232497</v>
+        <v>135063876</v>
       </c>
       <c r="B62" t="n">
-        <v>80438</v>
+        <v>99472</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7583,41 +7605,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>222812</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>499572</v>
+        <v>499672</v>
       </c>
       <c r="R62" t="n">
-        <v>6622131</v>
+        <v>6622314</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7641,17 +7659,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7666,19 +7689,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135063104</v>
+        <v>134232497</v>
       </c>
       <c r="B63" t="n">
         <v>80438</v>
@@ -7706,20 +7729,24 @@
           <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>499616</v>
+        <v>499572</v>
       </c>
       <c r="R63" t="n">
-        <v>6622213</v>
+        <v>6622131</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7743,27 +7770,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Vid basen av hänsynsasp.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7778,19 +7795,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135063382</v>
+        <v>135063104</v>
       </c>
       <c r="B64" t="n">
         <v>80438</v>
@@ -7825,10 +7842,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>499630</v>
+        <v>499616</v>
       </c>
       <c r="R64" t="n">
-        <v>6622258</v>
+        <v>6622213</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7860,7 +7877,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7870,12 +7887,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Basen på grav asp, ej hänsynssnitslad.</t>
+          <t>Vid basen av hänsynsasp.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7902,10 +7919,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135155821</v>
+        <v>135063382</v>
       </c>
       <c r="B65" t="n">
-        <v>57162</v>
+        <v>80438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7913,49 +7930,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bockhällen, Bockhällen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>499869</v>
+        <v>499630</v>
       </c>
       <c r="R65" t="n">
-        <v>6620679</v>
+        <v>6622258</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7982,17 +7984,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Fjäder.</t>
+          <t>Basen på grav asp, ej hänsynssnitslad.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8012,57 +8024,67 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Therese Steiner, Per Arneborn</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135155628</v>
+        <v>135155821</v>
       </c>
       <c r="B66" t="n">
-        <v>56706</v>
+        <v>57162</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>206046</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+          <t>Bockhällen, Bockhällen, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>499733</v>
+        <v>499869</v>
       </c>
       <c r="R66" t="n">
-        <v>6620805</v>
+        <v>6620679</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -8092,19 +8114,14 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>08:14</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>08:14</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fjäder.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8124,10 +8141,122 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
+          <t>Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135155628</v>
+      </c>
+      <c r="B67" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>499733</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6620805</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
           <t>Therese Steiner</t>
         </is>
       </c>
-      <c r="AY66" t="inlineStr"/>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -4489,7 +4489,7 @@
         <v>499579</v>
       </c>
       <c r="R35" t="n">
-        <v>6622252</v>
+        <v>6622251</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -5069,7 +5069,7 @@
         <v>499579</v>
       </c>
       <c r="R40" t="n">
-        <v>6622252</v>
+        <v>6622251</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -4489,7 +4489,7 @@
         <v>499579</v>
       </c>
       <c r="R35" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -5069,7 +5069,7 @@
         <v>499579</v>
       </c>
       <c r="R40" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122230880</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122230857</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122230848</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,10 +1092,15 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122230856</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135023647</v>
+        <v>135031428</v>
       </c>
       <c r="B6" t="n">
         <v>57162</v>
@@ -1104,31 +1129,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497636</v>
+        <v>497530</v>
       </c>
       <c r="R6" t="n">
-        <v>6621917</v>
+        <v>6621896</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1152,17 +1170,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fjäder från tjädertupp.</t>
+          <t>Vid rotvälta</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,38 +1201,28 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Våtmark med barrträd</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031428</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135031428</v>
+        <v>135032570</v>
       </c>
       <c r="B7" t="n">
         <v>57162</v>
@@ -1232,10 +1250,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1244,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497530</v>
+        <v>497665</v>
       </c>
       <c r="R7" t="n">
-        <v>6621896</v>
+        <v>6621899</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1279,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1289,12 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vid rotvälta</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,10 +1345,15 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135032570</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135032570</v>
+        <v>135033089</v>
       </c>
       <c r="B8" t="n">
         <v>57162</v>
@@ -1361,7 +1393,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1375,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497665</v>
+        <v>497769</v>
       </c>
       <c r="R8" t="n">
-        <v>6621899</v>
+        <v>6621851</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1410,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1452,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fjäder och färsk spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1481,15 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135033089</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135033089</v>
+        <v>135033156</v>
       </c>
       <c r="B9" t="n">
         <v>57162</v>
@@ -1475,24 +1517,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1501,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497769</v>
+        <v>497764</v>
       </c>
       <c r="R9" t="n">
-        <v>6621851</v>
+        <v>6621865</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1536,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fjäder och färsk spillning</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,13 +1598,18 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135033156</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135033156</v>
+        <v>135032906</v>
       </c>
       <c r="B10" t="n">
-        <v>57162</v>
+        <v>8449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,39 +1617,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497764</v>
+        <v>497759</v>
       </c>
       <c r="R10" t="n">
-        <v>6621865</v>
+        <v>6621852</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1653,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,13 +1715,18 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135032906</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135032906</v>
+        <v>135063650</v>
       </c>
       <c r="B11" t="n">
-        <v>8449</v>
+        <v>96629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,42 +1734,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497759</v>
+        <v>499668</v>
       </c>
       <c r="R11" t="n">
-        <v>6621852</v>
+        <v>6622263</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1760,22 +1804,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjolårskapslar. Anna Hammars fynd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,6 +1833,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1795,17 +1845,22 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063650</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135063650</v>
+        <v>135059885</v>
       </c>
       <c r="B12" t="n">
-        <v>96629</v>
+        <v>92370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,53 +1868,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>4217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499668</v>
+        <v>499491</v>
       </c>
       <c r="R12" t="n">
-        <v>6622263</v>
+        <v>6621469</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,12 +1937,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fjolårskapslar. Anna Hammars fynd.</t>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,7 +1951,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1928,13 +1966,18 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059885</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135059885</v>
+        <v>135060163</v>
       </c>
       <c r="B13" t="n">
-        <v>92370</v>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,21 +1985,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499491</v>
+        <v>499498</v>
       </c>
       <c r="R13" t="n">
-        <v>6621469</v>
+        <v>6621496</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2001,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,12 +2054,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På låga av tall</t>
+          <t>På 2 granlågor</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,10 +2083,15 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060163</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135060163</v>
+        <v>135060941</v>
       </c>
       <c r="B14" t="n">
         <v>91937</v>
@@ -2072,19 +2120,22 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499498</v>
+        <v>499512</v>
       </c>
       <c r="R14" t="n">
-        <v>6621496</v>
+        <v>6621487</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2111,51 +2162,42 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På 2 granlågor</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060941</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135060941</v>
+        <v>135063711</v>
       </c>
       <c r="B15" t="n">
         <v>91937</v>
@@ -2184,22 +2226,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499512</v>
+        <v>499668</v>
       </c>
       <c r="R15" t="n">
-        <v>6621487</v>
+        <v>6622269</v>
       </c>
       <c r="S15" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,40 +2265,54 @@
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063711</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135063711</v>
+        <v>135060050</v>
       </c>
       <c r="B16" t="n">
-        <v>91937</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,34 +2320,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499668</v>
+        <v>499490</v>
       </c>
       <c r="R16" t="n">
-        <v>6622269</v>
+        <v>6621488</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2326,7 +2384,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2394,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födohack på låga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2423,15 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060050</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135060050</v>
+        <v>135060358</v>
       </c>
       <c r="B17" t="n">
         <v>57972</v>
@@ -2403,10 +2471,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499490</v>
+        <v>499534</v>
       </c>
       <c r="R17" t="n">
-        <v>6621488</v>
+        <v>6621485</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2438,7 +2506,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,12 +2516,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Födohack på låga.</t>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2545,15 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060358</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135060358</v>
+        <v>135064630</v>
       </c>
       <c r="B18" t="n">
         <v>57972</v>
@@ -2516,14 +2589,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499534</v>
+        <v>499518</v>
       </c>
       <c r="R18" t="n">
-        <v>6621485</v>
+        <v>6622257</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2555,7 +2628,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,12 +2638,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:32</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På död gran.</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,10 +2662,15 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064630</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135064630</v>
+        <v>135064766</v>
       </c>
       <c r="B19" t="n">
         <v>57972</v>
@@ -2637,10 +2710,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499518</v>
+        <v>499448</v>
       </c>
       <c r="R19" t="n">
-        <v>6622257</v>
+        <v>6622215</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2672,7 +2745,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2682,7 +2755,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,30 +2779,35 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064766</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135064766</v>
+        <v>135061441</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2740,19 +2818,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499448</v>
+        <v>499547</v>
       </c>
       <c r="R20" t="n">
-        <v>6622215</v>
+        <v>6621734</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2784,7 +2862,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2794,7 +2872,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och små hackhål med savflöde i tall. Svårt att se på bild. Tallen utmärkt med rött band.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,41 +2901,46 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061441</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135061441</v>
+        <v>135059028</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2861,13 +2949,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499547</v>
+        <v>499383</v>
       </c>
       <c r="R21" t="n">
-        <v>6621734</v>
+        <v>6621640</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2896,7 +2984,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2906,12 +2994,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och små hackhål med savflöde i tall. Svårt att se på bild. Tallen utmärkt med rött band.</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2931,14 +3014,19 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059028</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135059028</v>
+        <v>135059664</v>
       </c>
       <c r="B22" t="n">
         <v>57162</v>
@@ -2974,17 +3062,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergsfallet, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499383</v>
+        <v>499413</v>
       </c>
       <c r="R22" t="n">
-        <v>6621640</v>
+        <v>6621371</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3013,7 +3101,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3023,7 +3111,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3135,15 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059664</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135059664</v>
+        <v>135061981</v>
       </c>
       <c r="B23" t="n">
         <v>57162</v>
@@ -3086,14 +3179,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartbergsfallet, Lindes sn, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499413</v>
+        <v>499563</v>
       </c>
       <c r="R23" t="n">
-        <v>6621371</v>
+        <v>6621889</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3125,7 +3218,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3135,7 +3228,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på häll bredvid hygget</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3257,15 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061981</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135061981</v>
+        <v>135062004</v>
       </c>
       <c r="B24" t="n">
         <v>57162</v>
@@ -3202,10 +3305,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499563</v>
+        <v>499575</v>
       </c>
       <c r="R24" t="n">
-        <v>6621889</v>
+        <v>6621902</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3237,7 +3340,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3247,12 +3350,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt på häll bredvid hygget</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3374,15 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135062004</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135062004</v>
+        <v>135062059</v>
       </c>
       <c r="B25" t="n">
         <v>57162</v>
@@ -3307,22 +3410,36 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499575</v>
+        <v>499546</v>
       </c>
       <c r="R25" t="n">
-        <v>6621902</v>
+        <v>6621943</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3354,7 +3471,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3364,7 +3481,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färsk fjäder fr tupp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3510,15 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135062059</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135062059</v>
+        <v>135062640</v>
       </c>
       <c r="B26" t="n">
         <v>57162</v>
@@ -3419,24 +3546,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3445,10 +3558,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499546</v>
+        <v>499562</v>
       </c>
       <c r="R26" t="n">
-        <v>6621943</v>
+        <v>6622064</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3480,7 +3593,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3490,12 +3603,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färsk fjäder fr tupp.</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3519,10 +3632,15 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135062640</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135062640</v>
+        <v>135064589</v>
       </c>
       <c r="B27" t="n">
         <v>57162</v>
@@ -3562,10 +3680,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499562</v>
+        <v>499561</v>
       </c>
       <c r="R27" t="n">
-        <v>6622064</v>
+        <v>6622261</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3597,7 +3715,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3607,12 +3725,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>I övergiven myrstack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,10 +3754,15 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064589</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135064589</v>
+        <v>135143988</v>
       </c>
       <c r="B28" t="n">
         <v>57162</v>
@@ -3667,22 +3790,33 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499561</v>
+        <v>499426</v>
       </c>
       <c r="R28" t="n">
-        <v>6622261</v>
+        <v>6621880</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3709,27 +3843,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I övergiven myrstack.</t>
+          <t>Uppflog tupp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,17 +3883,22 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135143988</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135143988</v>
+        <v>135060672</v>
       </c>
       <c r="B29" t="n">
-        <v>57162</v>
+        <v>4776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,50 +3906,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499426</v>
+        <v>499518</v>
       </c>
       <c r="R29" t="n">
-        <v>6621880</v>
+        <v>6621482</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3837,27 +3965,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Uppflog tupp</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,17 +4000,22 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060672</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135060672</v>
+        <v>135060532</v>
       </c>
       <c r="B30" t="n">
-        <v>4776</v>
+        <v>5181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,21 +4023,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3924,10 +4052,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499518</v>
+        <v>499516</v>
       </c>
       <c r="R30" t="n">
-        <v>6621482</v>
+        <v>6621486</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3959,7 +4087,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3969,7 +4097,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3993,56 +4121,60 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060532</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135060532</v>
+        <v>134232496</v>
       </c>
       <c r="B31" t="n">
-        <v>5181</v>
+        <v>58136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499516</v>
+        <v>499676</v>
       </c>
       <c r="R31" t="n">
-        <v>6621486</v>
+        <v>6622345</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4066,22 +4198,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4096,19 +4223,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232496</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134232496</v>
+        <v>135061152</v>
       </c>
       <c r="B32" t="n">
         <v>58136</v>
@@ -4141,19 +4273,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499676</v>
+        <v>499523</v>
       </c>
       <c r="R32" t="n">
-        <v>6622345</v>
+        <v>6621614</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4177,17 +4314,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4202,19 +4344,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061152</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135061152</v>
+        <v>135063205</v>
       </c>
       <c r="B33" t="n">
         <v>58136</v>
@@ -4249,19 +4396,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499523</v>
+        <v>499625</v>
       </c>
       <c r="R33" t="n">
-        <v>6621614</v>
+        <v>6622247</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4293,7 +4440,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4303,7 +4450,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4327,10 +4474,15 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063205</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135063205</v>
+        <v>135064184</v>
       </c>
       <c r="B34" t="n">
         <v>58136</v>
@@ -4358,26 +4510,22 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499625</v>
+        <v>499579</v>
       </c>
       <c r="R34" t="n">
-        <v>6622247</v>
+        <v>6622251</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4409,7 +4557,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4419,7 +4567,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4443,38 +4591,47 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064184</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135064184</v>
+        <v>135059398</v>
       </c>
       <c r="B35" t="n">
-        <v>58136</v>
+        <v>58131</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -4482,14 +4639,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499579</v>
+        <v>499378</v>
       </c>
       <c r="R35" t="n">
-        <v>6622252</v>
+        <v>6621540</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4521,7 +4678,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4531,7 +4688,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4555,10 +4712,15 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059398</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135059398</v>
+        <v>135063052</v>
       </c>
       <c r="B36" t="n">
         <v>58131</v>
@@ -4588,7 +4750,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4598,14 +4760,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499378</v>
+        <v>499604</v>
       </c>
       <c r="R36" t="n">
-        <v>6621540</v>
+        <v>6622206</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4637,7 +4799,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4647,7 +4809,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4671,10 +4833,15 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063052</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135063052</v>
+        <v>135063221</v>
       </c>
       <c r="B37" t="n">
         <v>58131</v>
@@ -4714,14 +4881,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499604</v>
+        <v>499629</v>
       </c>
       <c r="R37" t="n">
-        <v>6622206</v>
+        <v>6622247</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4753,7 +4920,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4763,7 +4930,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4787,10 +4954,15 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063221</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135063221</v>
+        <v>135063830</v>
       </c>
       <c r="B38" t="n">
         <v>58131</v>
@@ -4834,10 +5006,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499629</v>
+        <v>499665</v>
       </c>
       <c r="R38" t="n">
-        <v>6622247</v>
+        <v>6622296</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4869,7 +5041,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4879,7 +5051,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4903,10 +5075,15 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063830</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135063830</v>
+        <v>135064196</v>
       </c>
       <c r="B39" t="n">
         <v>58131</v>
@@ -4946,14 +5123,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499665</v>
+        <v>499579</v>
       </c>
       <c r="R39" t="n">
-        <v>6622296</v>
+        <v>6622251</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4985,7 +5162,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4995,7 +5172,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5019,13 +5196,18 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064196</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135064196</v>
+        <v>135060640</v>
       </c>
       <c r="B40" t="n">
-        <v>58131</v>
+        <v>5201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,16 +5215,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103023</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5050,26 +5232,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499579</v>
+        <v>499509</v>
       </c>
       <c r="R40" t="n">
-        <v>6622252</v>
+        <v>6621492</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5101,7 +5279,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5111,7 +5289,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5135,13 +5313,18 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060640</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135060640</v>
+        <v>135059764</v>
       </c>
       <c r="B41" t="n">
-        <v>5201</v>
+        <v>8449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,21 +5332,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5178,10 +5361,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499509</v>
+        <v>499467</v>
       </c>
       <c r="R41" t="n">
-        <v>6621492</v>
+        <v>6621437</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5213,7 +5396,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5223,7 +5406,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5247,41 +5430,46 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059764</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135059764</v>
+        <v>135059416</v>
       </c>
       <c r="B42" t="n">
-        <v>8449</v>
+        <v>56706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106554</v>
+        <v>206046</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5290,10 +5478,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499467</v>
+        <v>499365</v>
       </c>
       <c r="R42" t="n">
-        <v>6621437</v>
+        <v>6621528</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5325,7 +5513,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5335,7 +5523,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5359,10 +5547,15 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059416</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135059416</v>
+        <v>135062618</v>
       </c>
       <c r="B43" t="n">
         <v>56706</v>
@@ -5398,14 +5591,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499365</v>
+        <v>499537</v>
       </c>
       <c r="R43" t="n">
-        <v>6621528</v>
+        <v>6622009</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5437,7 +5630,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5447,7 +5640,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5471,56 +5664,60 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135062618</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135062618</v>
+        <v>133925272</v>
       </c>
       <c r="B44" t="n">
-        <v>56706</v>
+        <v>99112</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206046</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499537</v>
+        <v>499669</v>
       </c>
       <c r="R44" t="n">
-        <v>6622009</v>
+        <v>6622001</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5544,22 +5741,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5574,19 +5776,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133925272</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133925272</v>
+        <v>134232494</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5625,13 +5832,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499669</v>
+        <v>499476</v>
       </c>
       <c r="R45" t="n">
-        <v>6622001</v>
+        <v>6622065</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5658,19 +5865,9 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5699,10 +5896,15 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232494</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134232494</v>
+        <v>135059471</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5735,19 +5937,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499476</v>
+        <v>499368</v>
       </c>
       <c r="R46" t="n">
-        <v>6622065</v>
+        <v>6621511</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5771,17 +5983,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5796,19 +6013,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059471</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135059471</v>
+        <v>135060107</v>
       </c>
       <c r="B47" t="n">
         <v>99112</v>
@@ -5838,7 +6060,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5857,10 +6079,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499368</v>
+        <v>499479</v>
       </c>
       <c r="R47" t="n">
-        <v>6621511</v>
+        <v>6621502</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5892,7 +6114,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5902,7 +6124,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5926,10 +6148,15 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060107</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135060107</v>
+        <v>135060756</v>
       </c>
       <c r="B48" t="n">
         <v>99112</v>
@@ -5959,7 +6186,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5978,10 +6205,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499479</v>
+        <v>499547</v>
       </c>
       <c r="R48" t="n">
-        <v>6621502</v>
+        <v>6621511</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6013,7 +6240,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6023,7 +6250,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6047,10 +6274,15 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060756</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135060756</v>
+        <v>135061272</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -6080,7 +6312,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6099,10 +6331,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499547</v>
+        <v>499557</v>
       </c>
       <c r="R49" t="n">
-        <v>6621511</v>
+        <v>6621707</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6134,7 +6366,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6144,7 +6376,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6168,10 +6400,15 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061272</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135061272</v>
+        <v>135061286</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -6201,7 +6438,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6220,10 +6457,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499557</v>
+        <v>499553</v>
       </c>
       <c r="R50" t="n">
-        <v>6621707</v>
+        <v>6621728</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6255,7 +6492,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6265,7 +6502,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6289,10 +6526,15 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061286</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135061286</v>
+        <v>135061473</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -6322,32 +6564,30 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499553</v>
+        <v>499542</v>
       </c>
       <c r="R51" t="n">
-        <v>6621728</v>
+        <v>6621615</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6374,46 +6614,42 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061473</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135061473</v>
+        <v>135061528</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -6443,30 +6679,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499542</v>
+        <v>499602</v>
       </c>
       <c r="R52" t="n">
-        <v>6621615</v>
+        <v>6621752</v>
       </c>
       <c r="S52" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6493,37 +6731,51 @@
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061528</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135061528</v>
+        <v>135061587</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6553,7 +6805,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6572,10 +6824,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499602</v>
+        <v>499604</v>
       </c>
       <c r="R53" t="n">
-        <v>6621752</v>
+        <v>6621788</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6607,7 +6859,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6617,7 +6869,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6641,10 +6893,15 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061587</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135061587</v>
+        <v>135061709</v>
       </c>
       <c r="B54" t="n">
         <v>99112</v>
@@ -6674,7 +6931,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6693,10 +6950,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499604</v>
+        <v>499581</v>
       </c>
       <c r="R54" t="n">
-        <v>6621788</v>
+        <v>6621818</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6728,7 +6985,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6738,7 +6995,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6762,10 +7019,15 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061709</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135061709</v>
+        <v>135062653</v>
       </c>
       <c r="B55" t="n">
         <v>99112</v>
@@ -6795,7 +7057,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6810,14 +7072,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499581</v>
+        <v>499548</v>
       </c>
       <c r="R55" t="n">
-        <v>6621818</v>
+        <v>6622078</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6849,7 +7111,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6859,7 +7121,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6883,10 +7145,15 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135062653</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135062653</v>
+        <v>135064670</v>
       </c>
       <c r="B56" t="n">
         <v>99112</v>
@@ -6916,7 +7183,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6935,10 +7202,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499548</v>
+        <v>499511</v>
       </c>
       <c r="R56" t="n">
-        <v>6622078</v>
+        <v>6622238</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6970,7 +7237,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6980,7 +7247,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7004,10 +7271,15 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064670</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135064670</v>
+        <v>135138158</v>
       </c>
       <c r="B57" t="n">
         <v>99112</v>
@@ -7037,7 +7309,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7052,14 +7324,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499511</v>
+        <v>499412</v>
       </c>
       <c r="R57" t="n">
-        <v>6622238</v>
+        <v>6621454</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7086,22 +7358,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7121,17 +7393,22 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135138158</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135138158</v>
+        <v>135059208</v>
       </c>
       <c r="B58" t="n">
-        <v>99112</v>
+        <v>99219</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7139,26 +7416,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7168,7 +7445,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7177,10 +7454,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499412</v>
+        <v>499387</v>
       </c>
       <c r="R58" t="n">
-        <v>6621454</v>
+        <v>6621650</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7207,22 +7484,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7242,17 +7519,22 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059208</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135059208</v>
+        <v>135061615</v>
       </c>
       <c r="B59" t="n">
-        <v>99219</v>
+        <v>111153</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7260,33 +7542,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219847</v>
+        <v>220240</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7298,10 +7571,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499387</v>
+        <v>499604</v>
       </c>
       <c r="R59" t="n">
-        <v>6621650</v>
+        <v>6621787</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7333,7 +7606,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7343,7 +7616,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7367,13 +7645,18 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061615</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135061615</v>
+        <v>135063768</v>
       </c>
       <c r="B60" t="n">
-        <v>111153</v>
+        <v>98060</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7381,16 +7664,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220240</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7399,21 +7682,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>499604</v>
+        <v>499655</v>
       </c>
       <c r="R60" t="n">
-        <v>6621787</v>
+        <v>6622288</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7445,7 +7723,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7455,12 +7733,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7484,13 +7757,18 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063768</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135063768</v>
+        <v>135063876</v>
       </c>
       <c r="B61" t="n">
-        <v>98060</v>
+        <v>99472</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7498,16 +7776,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>222812</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7522,10 +7800,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>499655</v>
+        <v>499672</v>
       </c>
       <c r="R61" t="n">
-        <v>6622288</v>
+        <v>6622314</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7557,7 +7835,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7567,7 +7845,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7591,13 +7869,18 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063876</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135063876</v>
+        <v>134232497</v>
       </c>
       <c r="B62" t="n">
-        <v>99472</v>
+        <v>80438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7605,37 +7888,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222812</v>
+        <v>229497</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>499672</v>
+        <v>499572</v>
       </c>
       <c r="R62" t="n">
-        <v>6622314</v>
+        <v>6622131</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7659,22 +7946,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7689,19 +7971,24 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232497</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134232497</v>
+        <v>135063104</v>
       </c>
       <c r="B63" t="n">
         <v>80438</v>
@@ -7729,24 +8016,20 @@
           <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>499572</v>
+        <v>499616</v>
       </c>
       <c r="R63" t="n">
-        <v>6622131</v>
+        <v>6622213</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7770,17 +8053,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Vid basen av hänsynsasp.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7795,19 +8088,24 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063104</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135063104</v>
+        <v>135063382</v>
       </c>
       <c r="B64" t="n">
         <v>80438</v>
@@ -7842,10 +8140,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>499616</v>
+        <v>499630</v>
       </c>
       <c r="R64" t="n">
-        <v>6622213</v>
+        <v>6622258</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7877,7 +8175,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7887,12 +8185,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Vid basen av hänsynsasp.</t>
+          <t>Basen på grav asp, ej hänsynssnitslad.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7916,13 +8214,18 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063382</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135063382</v>
+        <v>135155821</v>
       </c>
       <c r="B65" t="n">
-        <v>80438</v>
+        <v>57162</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7930,34 +8233,49 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bockhällen, Bockhällen, Vstm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>499630</v>
+        <v>499869</v>
       </c>
       <c r="R65" t="n">
-        <v>6622258</v>
+        <v>6620679</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7984,27 +8302,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Basen på grav asp, ej hänsynssnitslad.</t>
+          <t>Fjäder.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8024,67 +8332,62 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner, Per Arneborn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135155821</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135155821</v>
+        <v>135155628</v>
       </c>
       <c r="B66" t="n">
-        <v>57162</v>
+        <v>56706</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>206046</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bockhällen, Bockhällen, Vstm</t>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>499869</v>
+        <v>499733</v>
       </c>
       <c r="R66" t="n">
-        <v>6620679</v>
+        <v>6620805</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -8114,14 +8417,19 @@
           <t>2026-07-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Fjäder.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8141,124 +8449,84 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Therese Steiner, Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135155628</v>
-      </c>
-      <c r="B67" t="n">
-        <v>56706</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>206046</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Alces alces</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>499733</v>
-      </c>
-      <c r="R67" t="n">
-        <v>6620805</v>
-      </c>
-      <c r="S67" t="n">
-        <v>20</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Lindesberg</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>08:14</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>08:14</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135155628</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -4525,7 +4525,7 @@
         <v>499579</v>
       </c>
       <c r="R34" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -5130,7 +5130,7 @@
         <v>499579</v>
       </c>
       <c r="R39" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ66"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135031428</v>
+        <v>135023647</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,24 +1129,31 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497530</v>
+        <v>497636</v>
       </c>
       <c r="R6" t="n">
-        <v>6621896</v>
+        <v>6621917</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,27 +1177,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vid rotvälta</t>
+          <t>Fjäder från tjädertupp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,31 +1198,46 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Våtmark med barrträd</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031428</t>
+          <t>https://artportalen.se/Sighting/135023647</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135032570</v>
+        <v>135031428</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,24 +1262,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1276,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497665</v>
+        <v>497530</v>
       </c>
       <c r="R7" t="n">
-        <v>6621899</v>
+        <v>6621896</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1311,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1319,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid rotvälta</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,16 +1350,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135032570</t>
+          <t>https://artportalen.se/Sighting/135031428</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135033089</v>
+        <v>135032570</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1396,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1407,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497769</v>
+        <v>497665</v>
       </c>
       <c r="R8" t="n">
-        <v>6621851</v>
+        <v>6621899</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1442,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,12 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fjäder och färsk spillning</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,16 +1481,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135033089</t>
+          <t>https://artportalen.se/Sighting/135032570</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135033156</v>
+        <v>135033089</v>
       </c>
       <c r="B9" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,10 +1515,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497764</v>
+        <v>497769</v>
       </c>
       <c r="R9" t="n">
-        <v>6621865</v>
+        <v>6621851</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1564,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1586,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjäder och färsk spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,16 +1617,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135033156</t>
+          <t>https://artportalen.se/Sighting/135033089</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135032906</v>
+        <v>135033156</v>
       </c>
       <c r="B10" t="n">
-        <v>8449</v>
+        <v>57167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,39 +1634,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497759</v>
+        <v>497764</v>
       </c>
       <c r="R10" t="n">
-        <v>6621852</v>
+        <v>6621865</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1681,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1708,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,16 +1734,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135032906</t>
+          <t>https://artportalen.se/Sighting/135033156</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135063650</v>
+        <v>135032906</v>
       </c>
       <c r="B11" t="n">
-        <v>96629</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,53 +1751,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499668</v>
+        <v>497759</v>
       </c>
       <c r="R11" t="n">
-        <v>6622263</v>
+        <v>6621852</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,27 +1810,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fjolårskapslar. Anna Hammars fynd.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,7 +1834,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1845,22 +1845,22 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135063650</t>
+          <t>https://artportalen.se/Sighting/135032906</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135059885</v>
+        <v>135063650</v>
       </c>
       <c r="B12" t="n">
-        <v>92370</v>
+        <v>96673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,37 +1868,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499491</v>
+        <v>499668</v>
       </c>
       <c r="R12" t="n">
-        <v>6621469</v>
+        <v>6622263</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1927,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,12 +1953,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På låga av tall</t>
+          <t>Fjolårskapslar. Anna Hammars fynd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,6 +1967,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1968,16 +1985,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135059885</t>
+          <t>https://artportalen.se/Sighting/135063650</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135060163</v>
+        <v>135059885</v>
       </c>
       <c r="B13" t="n">
-        <v>91937</v>
+        <v>92412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,21 +2002,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2009,10 +2026,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499498</v>
+        <v>499491</v>
       </c>
       <c r="R13" t="n">
-        <v>6621496</v>
+        <v>6621469</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2044,7 +2061,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,12 +2071,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På 2 granlågor</t>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2085,16 +2102,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135060163</t>
+          <t>https://artportalen.se/Sighting/135059885</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135060941</v>
+        <v>135060163</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,22 +2137,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499512</v>
+        <v>499498</v>
       </c>
       <c r="R14" t="n">
-        <v>6621487</v>
+        <v>6621496</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,45 +2176,59 @@
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På 2 granlågor</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135060941</t>
+          <t>https://artportalen.se/Sighting/135060163</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135063711</v>
+        <v>135060941</v>
       </c>
       <c r="B15" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,19 +2254,22 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499668</v>
+        <v>499512</v>
       </c>
       <c r="R15" t="n">
-        <v>6622269</v>
+        <v>6621487</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2265,54 +2296,45 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135063711</t>
+          <t>https://artportalen.se/Sighting/135060941</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135060050</v>
+        <v>135063711</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>91979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2320,39 +2342,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499490</v>
+        <v>499668</v>
       </c>
       <c r="R16" t="n">
-        <v>6621488</v>
+        <v>6622269</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2384,7 +2401,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2394,12 +2411,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födohack på låga.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,16 +2437,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135060050</t>
+          <t>https://artportalen.se/Sighting/135063711</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135060358</v>
+        <v>135060050</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,10 +2483,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499534</v>
+        <v>499490</v>
       </c>
       <c r="R17" t="n">
-        <v>6621485</v>
+        <v>6621488</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2506,7 +2518,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2516,12 +2528,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>Födohack på låga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,16 +2559,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135060358</t>
+          <t>https://artportalen.se/Sighting/135060050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135064630</v>
+        <v>135060358</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,14 +2601,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499518</v>
+        <v>499534</v>
       </c>
       <c r="R18" t="n">
-        <v>6622257</v>
+        <v>6621485</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2628,7 +2640,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2638,7 +2650,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2664,16 +2681,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135064630</t>
+          <t>https://artportalen.se/Sighting/135060358</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135064766</v>
+        <v>135064630</v>
       </c>
       <c r="B19" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,10 +2727,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499448</v>
+        <v>499518</v>
       </c>
       <c r="R19" t="n">
-        <v>6622215</v>
+        <v>6622257</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2745,7 +2762,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2755,7 +2772,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2781,33 +2798,33 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135064766</t>
+          <t>https://artportalen.se/Sighting/135064630</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135061441</v>
+        <v>135064766</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2818,19 +2835,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499547</v>
+        <v>499448</v>
       </c>
       <c r="R20" t="n">
-        <v>6621734</v>
+        <v>6622215</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2862,7 +2879,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2872,12 +2889,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack och små hackhål med savflöde i tall. Svårt att se på bild. Tallen utmärkt med rött band.</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,44 +2915,44 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135061441</t>
+          <t>https://artportalen.se/Sighting/135064766</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135059028</v>
+        <v>135061441</v>
       </c>
       <c r="B21" t="n">
-        <v>57162</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2949,13 +2961,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499383</v>
+        <v>499547</v>
       </c>
       <c r="R21" t="n">
-        <v>6621640</v>
+        <v>6621734</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2984,7 +2996,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2994,7 +3006,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och små hackhål med savflöde i tall. Svårt att se på bild. Tallen utmärkt med rött band.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,16 +3037,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135059028</t>
+          <t>https://artportalen.se/Sighting/135061441</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135059664</v>
+        <v>135059028</v>
       </c>
       <c r="B22" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,17 +3079,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartbergsfallet, Lindes sn, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499413</v>
+        <v>499383</v>
       </c>
       <c r="R22" t="n">
-        <v>6621371</v>
+        <v>6621640</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3101,7 +3118,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3111,7 +3128,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,16 +3154,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135059664</t>
+          <t>https://artportalen.se/Sighting/135059028</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135061981</v>
+        <v>135059664</v>
       </c>
       <c r="B23" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3179,14 +3196,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergsfallet, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499563</v>
+        <v>499413</v>
       </c>
       <c r="R23" t="n">
-        <v>6621889</v>
+        <v>6621371</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3218,7 +3235,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3228,12 +3245,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt på häll bredvid hygget</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3259,16 +3271,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135061981</t>
+          <t>https://artportalen.se/Sighting/135059664</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135062004</v>
+        <v>135061981</v>
       </c>
       <c r="B24" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3305,10 +3317,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499575</v>
+        <v>499563</v>
       </c>
       <c r="R24" t="n">
-        <v>6621902</v>
+        <v>6621889</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3340,7 +3352,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3350,7 +3362,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt på häll bredvid hygget</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3376,16 +3393,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135062004</t>
+          <t>https://artportalen.se/Sighting/135061981</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135062059</v>
+        <v>135062004</v>
       </c>
       <c r="B25" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3410,36 +3427,22 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499546</v>
+        <v>499575</v>
       </c>
       <c r="R25" t="n">
-        <v>6621943</v>
+        <v>6621902</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3471,7 +3474,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3481,12 +3484,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färsk fjäder fr tupp.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3512,16 +3510,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135062059</t>
+          <t>https://artportalen.se/Sighting/135062004</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135062640</v>
+        <v>135062059</v>
       </c>
       <c r="B26" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,10 +3544,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3558,10 +3570,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499562</v>
+        <v>499546</v>
       </c>
       <c r="R26" t="n">
-        <v>6622064</v>
+        <v>6621943</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3593,7 +3605,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3603,12 +3615,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Färsk fjäder fr tupp.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3634,16 +3646,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135062640</t>
+          <t>https://artportalen.se/Sighting/135062059</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135064589</v>
+        <v>135062640</v>
       </c>
       <c r="B27" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3680,10 +3692,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499561</v>
+        <v>499562</v>
       </c>
       <c r="R27" t="n">
-        <v>6622261</v>
+        <v>6622064</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3715,7 +3727,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3725,12 +3737,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I övergiven myrstack.</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3756,16 +3768,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135064589</t>
+          <t>https://artportalen.se/Sighting/135062640</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135143988</v>
+        <v>135064589</v>
       </c>
       <c r="B28" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,33 +3802,22 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499426</v>
+        <v>499561</v>
       </c>
       <c r="R28" t="n">
-        <v>6621880</v>
+        <v>6622261</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3843,27 +3844,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Uppflog tupp</t>
+          <t>I övergiven myrstack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3883,22 +3884,22 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135143988</t>
+          <t>https://artportalen.se/Sighting/135064589</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135060672</v>
+        <v>135143988</v>
       </c>
       <c r="B29" t="n">
-        <v>4776</v>
+        <v>57167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3906,39 +3907,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499518</v>
+        <v>499426</v>
       </c>
       <c r="R29" t="n">
-        <v>6621482</v>
+        <v>6621880</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3965,22 +3977,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppflog tupp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4000,22 +4017,22 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135060672</t>
+          <t>https://artportalen.se/Sighting/135143988</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135060532</v>
+        <v>135060672</v>
       </c>
       <c r="B30" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4023,21 +4040,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4052,10 +4069,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499516</v>
+        <v>499518</v>
       </c>
       <c r="R30" t="n">
-        <v>6621486</v>
+        <v>6621482</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4087,7 +4104,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4097,7 +4114,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4123,58 +4140,59 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135060532</t>
+          <t>https://artportalen.se/Sighting/135060672</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134232496</v>
+        <v>135060532</v>
       </c>
       <c r="B31" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499676</v>
+        <v>499516</v>
       </c>
       <c r="R31" t="n">
-        <v>6622345</v>
+        <v>6621486</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4198,17 +4216,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4223,24 +4246,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232496</t>
+          <t>https://artportalen.se/Sighting/135060532</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135061152</v>
+        <v>134232496</v>
       </c>
       <c r="B32" t="n">
         <v>58136</v>
@@ -4273,24 +4296,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499523</v>
+        <v>499676</v>
       </c>
       <c r="R32" t="n">
-        <v>6621614</v>
+        <v>6622345</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4314,22 +4332,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4344,27 +4357,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135061152</t>
+          <t>https://artportalen.se/Sighting/134232496</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135063205</v>
+        <v>135061152</v>
       </c>
       <c r="B33" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4396,19 +4409,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499625</v>
+        <v>499523</v>
       </c>
       <c r="R33" t="n">
-        <v>6622247</v>
+        <v>6621614</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4440,7 +4453,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4450,7 +4463,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4476,16 +4489,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135063205</t>
+          <t>https://artportalen.se/Sighting/135061152</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135064184</v>
+        <v>135063205</v>
       </c>
       <c r="B34" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4510,22 +4523,26 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499579</v>
+        <v>499625</v>
       </c>
       <c r="R34" t="n">
-        <v>6622252</v>
+        <v>6622247</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4557,7 +4574,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4567,7 +4584,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4593,45 +4610,41 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135064184</t>
+          <t>https://artportalen.se/Sighting/135063205</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135059398</v>
+        <v>135064184</v>
       </c>
       <c r="B35" t="n">
-        <v>58131</v>
+        <v>58141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -4639,14 +4652,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499378</v>
+        <v>499579</v>
       </c>
       <c r="R35" t="n">
-        <v>6621540</v>
+        <v>6622252</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4678,7 +4691,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4688,7 +4701,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4708,22 +4721,22 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135059398</t>
+          <t>https://artportalen.se/Sighting/135064184</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135063052</v>
+        <v>135059398</v>
       </c>
       <c r="B36" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4750,7 +4763,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4760,14 +4773,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499604</v>
+        <v>499378</v>
       </c>
       <c r="R36" t="n">
-        <v>6622206</v>
+        <v>6621540</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4799,7 +4812,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4809,7 +4822,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4835,16 +4848,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135063052</t>
+          <t>https://artportalen.se/Sighting/135059398</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135063221</v>
+        <v>135063052</v>
       </c>
       <c r="B37" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4881,14 +4894,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499629</v>
+        <v>499604</v>
       </c>
       <c r="R37" t="n">
-        <v>6622247</v>
+        <v>6622206</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4920,7 +4933,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4930,7 +4943,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4956,16 +4969,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135063221</t>
+          <t>https://artportalen.se/Sighting/135063052</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135063830</v>
+        <v>135063221</v>
       </c>
       <c r="B38" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5006,10 +5019,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499665</v>
+        <v>499629</v>
       </c>
       <c r="R38" t="n">
-        <v>6622296</v>
+        <v>6622247</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -5041,7 +5054,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5051,7 +5064,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5077,16 +5090,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135063830</t>
+          <t>https://artportalen.se/Sighting/135063221</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135064196</v>
+        <v>135063830</v>
       </c>
       <c r="B39" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5123,14 +5136,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499579</v>
+        <v>499665</v>
       </c>
       <c r="R39" t="n">
-        <v>6622252</v>
+        <v>6622296</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -5162,7 +5175,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5172,7 +5185,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5198,16 +5211,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135064196</t>
+          <t>https://artportalen.se/Sighting/135063830</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135060640</v>
+        <v>135064196</v>
       </c>
       <c r="B40" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5215,16 +5228,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5232,22 +5245,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499509</v>
+        <v>499579</v>
       </c>
       <c r="R40" t="n">
-        <v>6621492</v>
+        <v>6622252</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5279,7 +5296,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5289,7 +5306,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5309,22 +5326,22 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135060640</t>
+          <t>https://artportalen.se/Sighting/135064196</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135059764</v>
+        <v>135060640</v>
       </c>
       <c r="B41" t="n">
-        <v>8449</v>
+        <v>5201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5332,21 +5349,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5361,10 +5378,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499467</v>
+        <v>499509</v>
       </c>
       <c r="R41" t="n">
-        <v>6621437</v>
+        <v>6621492</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5396,7 +5413,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5406,7 +5423,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5432,44 +5449,44 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135059764</t>
+          <t>https://artportalen.se/Sighting/135060640</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135059416</v>
+        <v>135059764</v>
       </c>
       <c r="B42" t="n">
-        <v>56706</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>206046</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5478,10 +5495,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499365</v>
+        <v>499467</v>
       </c>
       <c r="R42" t="n">
-        <v>6621528</v>
+        <v>6621437</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5513,7 +5530,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5523,7 +5540,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5549,16 +5566,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135059416</t>
+          <t>https://artportalen.se/Sighting/135059764</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135062618</v>
+        <v>135059416</v>
       </c>
       <c r="B43" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5591,14 +5608,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499537</v>
+        <v>499365</v>
       </c>
       <c r="R43" t="n">
-        <v>6622009</v>
+        <v>6621528</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5630,7 +5647,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5640,7 +5657,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5666,58 +5683,59 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135062618</t>
+          <t>https://artportalen.se/Sighting/135059416</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133925272</v>
+        <v>135062618</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>56711</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>206046</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499669</v>
+        <v>499537</v>
       </c>
       <c r="R44" t="n">
-        <v>6622001</v>
+        <v>6622009</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5741,27 +5759,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5776,24 +5789,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133925272</t>
+          <t>https://artportalen.se/Sighting/135062618</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134232494</v>
+        <v>133925272</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5832,13 +5845,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499476</v>
+        <v>499669</v>
       </c>
       <c r="R45" t="n">
-        <v>6622065</v>
+        <v>6622001</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5865,9 +5878,19 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5898,13 +5921,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232494</t>
+          <t>https://artportalen.se/Sighting/133925272</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135059471</v>
+        <v>134232494</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5937,29 +5960,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499368</v>
+        <v>499476</v>
       </c>
       <c r="R46" t="n">
-        <v>6621511</v>
+        <v>6622065</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5983,22 +5996,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6013,27 +6021,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135059471</t>
+          <t>https://artportalen.se/Sighting/134232494</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135060107</v>
+        <v>135059471</v>
       </c>
       <c r="B47" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6060,7 +6068,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6079,10 +6087,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499479</v>
+        <v>499368</v>
       </c>
       <c r="R47" t="n">
-        <v>6621502</v>
+        <v>6621511</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -6114,7 +6122,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6124,7 +6132,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6150,16 +6158,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135060107</t>
+          <t>https://artportalen.se/Sighting/135059471</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135060756</v>
+        <v>135060107</v>
       </c>
       <c r="B48" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6186,7 +6194,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6205,10 +6213,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499547</v>
+        <v>499479</v>
       </c>
       <c r="R48" t="n">
-        <v>6621511</v>
+        <v>6621502</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6240,7 +6248,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6250,7 +6258,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6276,16 +6284,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135060756</t>
+          <t>https://artportalen.se/Sighting/135060107</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135061272</v>
+        <v>135060756</v>
       </c>
       <c r="B49" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6312,7 +6320,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6331,10 +6339,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499557</v>
+        <v>499547</v>
       </c>
       <c r="R49" t="n">
-        <v>6621707</v>
+        <v>6621511</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6366,7 +6374,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6376,7 +6384,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6402,16 +6410,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135061272</t>
+          <t>https://artportalen.se/Sighting/135060756</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135061286</v>
+        <v>135061272</v>
       </c>
       <c r="B50" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6438,7 +6446,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6457,10 +6465,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499553</v>
+        <v>499557</v>
       </c>
       <c r="R50" t="n">
-        <v>6621728</v>
+        <v>6621707</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6492,7 +6500,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6502,7 +6510,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6528,16 +6536,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135061286</t>
+          <t>https://artportalen.se/Sighting/135061272</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135061473</v>
+        <v>135061286</v>
       </c>
       <c r="B51" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6564,30 +6572,32 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499542</v>
+        <v>499553</v>
       </c>
       <c r="R51" t="n">
-        <v>6621615</v>
+        <v>6621728</v>
       </c>
       <c r="S51" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6614,45 +6624,54 @@
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135061473</t>
+          <t>https://artportalen.se/Sighting/135061286</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135061528</v>
+        <v>135061473</v>
       </c>
       <c r="B52" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6679,32 +6698,30 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499602</v>
+        <v>499542</v>
       </c>
       <c r="R52" t="n">
-        <v>6621752</v>
+        <v>6621615</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6731,54 +6748,45 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135061528</t>
+          <t>https://artportalen.se/Sighting/135061473</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135061587</v>
+        <v>135061528</v>
       </c>
       <c r="B53" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6805,7 +6813,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6824,10 +6832,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499604</v>
+        <v>499602</v>
       </c>
       <c r="R53" t="n">
-        <v>6621788</v>
+        <v>6621752</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6859,7 +6867,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6869,7 +6877,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6895,16 +6903,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135061587</t>
+          <t>https://artportalen.se/Sighting/135061528</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135061709</v>
+        <v>135061587</v>
       </c>
       <c r="B54" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6931,7 +6939,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6950,10 +6958,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499581</v>
+        <v>499604</v>
       </c>
       <c r="R54" t="n">
-        <v>6621818</v>
+        <v>6621788</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6985,7 +6993,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6995,7 +7003,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7021,16 +7029,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135061709</t>
+          <t>https://artportalen.se/Sighting/135061587</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135062653</v>
+        <v>135061709</v>
       </c>
       <c r="B55" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7057,7 +7065,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7072,14 +7080,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>499548</v>
+        <v>499581</v>
       </c>
       <c r="R55" t="n">
-        <v>6622078</v>
+        <v>6621818</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -7111,7 +7119,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7121,7 +7129,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7147,16 +7155,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135062653</t>
+          <t>https://artportalen.se/Sighting/135061709</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135064670</v>
+        <v>135062653</v>
       </c>
       <c r="B56" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7183,7 +7191,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7202,10 +7210,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>499511</v>
+        <v>499548</v>
       </c>
       <c r="R56" t="n">
-        <v>6622238</v>
+        <v>6622078</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -7237,7 +7245,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7247,7 +7255,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7273,16 +7281,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135064670</t>
+          <t>https://artportalen.se/Sighting/135062653</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135138158</v>
+        <v>135064670</v>
       </c>
       <c r="B57" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7309,7 +7317,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7324,14 +7332,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>499412</v>
+        <v>499511</v>
       </c>
       <c r="R57" t="n">
-        <v>6621454</v>
+        <v>6622238</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7358,22 +7366,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7393,22 +7401,22 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135138158</t>
+          <t>https://artportalen.se/Sighting/135064670</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135059208</v>
+        <v>135138158</v>
       </c>
       <c r="B58" t="n">
-        <v>99219</v>
+        <v>99159</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7416,26 +7424,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7445,7 +7453,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7454,10 +7462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>499387</v>
+        <v>499412</v>
       </c>
       <c r="R58" t="n">
-        <v>6621650</v>
+        <v>6621454</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7484,22 +7492,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7519,22 +7527,22 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135059208</t>
+          <t>https://artportalen.se/Sighting/135138158</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135061615</v>
+        <v>135059208</v>
       </c>
       <c r="B59" t="n">
-        <v>111153</v>
+        <v>99266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7542,24 +7550,33 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220240</v>
+        <v>219847</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7571,10 +7588,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>499604</v>
+        <v>499387</v>
       </c>
       <c r="R59" t="n">
-        <v>6621787</v>
+        <v>6621650</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7606,7 +7623,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7616,12 +7633,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7647,16 +7659,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135061615</t>
+          <t>https://artportalen.se/Sighting/135059208</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135063768</v>
+        <v>135061615</v>
       </c>
       <c r="B60" t="n">
-        <v>98060</v>
+        <v>111210</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7664,16 +7676,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>220240</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7682,16 +7694,21 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>499655</v>
+        <v>499604</v>
       </c>
       <c r="R60" t="n">
-        <v>6622288</v>
+        <v>6621787</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7723,7 +7740,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7733,7 +7750,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7759,16 +7781,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135063768</t>
+          <t>https://artportalen.se/Sighting/135061615</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135063876</v>
+        <v>135063768</v>
       </c>
       <c r="B61" t="n">
-        <v>99472</v>
+        <v>98104</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7776,16 +7798,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222812</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7800,10 +7822,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>499672</v>
+        <v>499655</v>
       </c>
       <c r="R61" t="n">
-        <v>6622314</v>
+        <v>6622288</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7835,7 +7857,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7845,7 +7867,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7871,16 +7893,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135063876</t>
+          <t>https://artportalen.se/Sighting/135063768</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134232497</v>
+        <v>135063876</v>
       </c>
       <c r="B62" t="n">
-        <v>80438</v>
+        <v>99519</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7888,41 +7910,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>222812</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>499572</v>
+        <v>499672</v>
       </c>
       <c r="R62" t="n">
-        <v>6622131</v>
+        <v>6622314</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7946,17 +7964,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7971,24 +7994,24 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232497</t>
+          <t>https://artportalen.se/Sighting/135063876</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135063104</v>
+        <v>134232497</v>
       </c>
       <c r="B63" t="n">
         <v>80438</v>
@@ -8016,20 +8039,24 @@
           <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>499616</v>
+        <v>499572</v>
       </c>
       <c r="R63" t="n">
-        <v>6622213</v>
+        <v>6622131</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8053,27 +8080,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Vid basen av hänsynsasp.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8088,27 +8105,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135063104</t>
+          <t>https://artportalen.se/Sighting/134232497</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135063382</v>
+        <v>135063104</v>
       </c>
       <c r="B64" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8140,10 +8157,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>499630</v>
+        <v>499616</v>
       </c>
       <c r="R64" t="n">
-        <v>6622258</v>
+        <v>6622213</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -8175,7 +8192,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8185,12 +8202,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Basen på grav asp, ej hänsynssnitslad.</t>
+          <t>Vid basen av hänsynsasp.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8216,16 +8233,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135063382</t>
+          <t>https://artportalen.se/Sighting/135063104</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135155821</v>
+        <v>135063382</v>
       </c>
       <c r="B65" t="n">
-        <v>57162</v>
+        <v>80476</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8233,49 +8250,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bockhällen, Bockhällen, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>499869</v>
+        <v>499630</v>
       </c>
       <c r="R65" t="n">
-        <v>6620679</v>
+        <v>6622258</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -8302,17 +8304,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Fjäder.</t>
+          <t>Basen på grav asp, ej hänsynssnitslad.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8332,62 +8344,72 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Therese Steiner, Per Arneborn</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135155821</t>
+          <t>https://artportalen.se/Sighting/135063382</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135155628</v>
+        <v>135155821</v>
       </c>
       <c r="B66" t="n">
-        <v>56706</v>
+        <v>57167</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>206046</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+          <t>Bockhällen, Bockhällen, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>499733</v>
+        <v>499869</v>
       </c>
       <c r="R66" t="n">
-        <v>6620805</v>
+        <v>6620679</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -8417,19 +8439,14 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>08:14</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>08:14</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fjäder.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8449,11 +8466,128 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Therese Steiner, Per Arneborn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135155821</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135155628</v>
+      </c>
+      <c r="B67" t="n">
+        <v>56711</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svartbergsfallet, Svartbergsfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>499733</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6620805</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135155628</t>
         </is>
@@ -8526,6 +8660,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -1860,7 +1860,7 @@
         <v>135063650</v>
       </c>
       <c r="B12" t="n">
-        <v>96673</v>
+        <v>96700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>135059885</v>
       </c>
       <c r="B13" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135060163</v>
       </c>
       <c r="B14" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>135060941</v>
       </c>
       <c r="B15" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135063711</v>
       </c>
       <c r="B16" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135059471</v>
       </c>
       <c r="B47" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>135060107</v>
       </c>
       <c r="B48" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>135060756</v>
       </c>
       <c r="B49" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>135061272</v>
       </c>
       <c r="B50" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>135061286</v>
       </c>
       <c r="B51" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>135061473</v>
       </c>
       <c r="B52" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135061528</v>
       </c>
       <c r="B53" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>135061587</v>
       </c>
       <c r="B54" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>135061709</v>
       </c>
       <c r="B55" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>135062653</v>
       </c>
       <c r="B56" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>135064670</v>
       </c>
       <c r="B57" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>135138158</v>
       </c>
       <c r="B58" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>135059208</v>
       </c>
       <c r="B59" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>135061615</v>
       </c>
       <c r="B60" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>135063768</v>
       </c>
       <c r="B61" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>135063876</v>
       </c>
       <c r="B62" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>135063104</v>
       </c>
       <c r="B64" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>135063382</v>
       </c>
       <c r="B65" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 396-2024 artfynd.xlsx
+++ b/artfynd/S 396-2024 artfynd.xlsx
@@ -4721,7 +4721,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
